--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Розподіл розділів" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_horbonos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -82,6 +83,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -598,4 +602,64 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ID/локатор</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Пункт чек-листа</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Цитата</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Виправлення</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Хто знайшов</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -48,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -70,11 +70,25 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +99,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,56 +636,492 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>ID/локатор</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Критерій</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Пункт чек-листа</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Цитата</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Виправлення</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Хто знайшов</t>
         </is>
       </c>
-    </row>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Рядків</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>F-20</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>п. 2 (вимога чітка і зрозуміла), п. 4 (допускає єдину інтерпретацію). Цільова сторінка не названа, тож тест-кейс має кілька «очікуваних результатів».</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>«Після успішного входу система перенаправляє користувача на відповідну сторінку.»</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>«Після успішного входу система перенаправляє покупця на сторінку особистого кабінету (/account); якщо вхід виконано на кроці «Sign in» оформлення замовлення (F-110) — на крок «Billing Address».»</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="J2" s="8">
+        <f>COUNTIF($C$2:$C$11,I2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>F-60</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>п. 4 (допускає єдину інтерпретацію), п. 3 (трактується в сенсі автора). «Схожі» не задає правила збігу: підрядок, нечіткий пошук чи синоніми.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>«Поле пошуку на головній сторінці дозволяє знайти товари, назви яких схожі на введений запит.»</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>«Поле пошуку на головній сторінці дозволяє знайти товари, назви яких містять введений запит (без урахування регістру літер).» (Правило звірено з demo: запит «PLI» повертає «Pliers», «Combination Pliers» та інші.)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="J3" s="8">
+        <f>COUNTIF($C$2:$C$11,I3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>F-100</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>п. 3 (немає посилань на неіснуючі документи). У розділі 5 є вимоги BL-10…BL-80 з кроком 10; BL-25 немає.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>«Обмеження на кількість одиниць у рядку визначає вимога BL-25.»</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>«Обмеження на кількість одиниць у рядку (ціле число від 1 до 99 включно) визначає вимога BL-40.»</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="J4" s="8">
+        <f>COUNTIF($C$2:$C$11,I4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>F-140</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>п. 4 (обумовлено всі допустимі та недопустимі вхідні дані), п. 5 (реакція на помилки). Для вкладення не задано формат, розмір і реакцію на недопустимий файл.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>«До звернення можна додати файл-вкладення.»</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>«До звернення можна додати один файл-вкладення розміром до 5 МБ у форматі PDF, PNG, JPG або TXT; для файлу, що не відповідає цим умовам, система показує повідомлення про недопустимий файл біля поля вкладення і не надсилає звернення (GUI-50).» (Формати й межа 5 МБ — потребує підтвердження замовником.)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="J5" s="8">
+        <f>COUNTIF($C$2:$C$11,I5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>F-110 ↔ BL-60</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній). Різний поріг безкоштовної доставки; у F-110 також не вказано, до чи після знижки рахується сума.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>F-110: «для замовлень від 2000 грн доставка безкоштовна». BL-60: «0.00 грн, якщо сума після знижки не менша за 1500 грн».</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>У F-110: «… вартість доставки: 120 грн; якщо сума замовлення після знижки за обсяг становить не менше 1500 грн, доставка безкоштовна.» (Поріг 1500 грн узято з BL-60 — потребує підтвердження замовником.)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="J6" s="8">
+        <f>COUNTIF($C$2:$C$11,I6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>F-120 ↔ GUI-40</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній). На користь правки F-120: 1.3 («Обране» — збережені зареєстрованим покупцем) і 2.1 (обране лише в ролі «Зареєстрований покупець»).</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>F-120: «Покупець може додати товар до списку обраного кнопкою «Add to favourites» без входу в систему». GUI-40: «якщо покупець не увійшов у систему, … товар до обраного не додається».</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>У F-120: «Зареєстрований покупець, який увійшов у систему, може додати товар до списку обраного кнопкою «Add to favourites»; для неавторизованого покупця поведінку визначає GUI-40. Список обраного доступний у кабінеті («My favorites»), де позицію можна видалити.»</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="J7" s="8">
+        <f>COUNTIF($C$2:$C$11,I7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>F-40 ↔ GUI-20</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній). Різна кількість карток на сторінці; на demo каталог показує 9 карток (сітка 3×3), тож правиться GUI-20.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>F-40: «по 9 карток на сторінці». GUI-20: «у три колонки по 12 карток на сторінці».</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>У GUI-20: «Картки каталогу розміщуються сіткою у три колонки по 9 карток на сторінці; картка містить зображення, назву, шкалу класу CO2 і ціну; для відсутнього товару поверх зображення виводиться позначка «Out of stock».»</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="J8" s="9">
+        <f>SUM(J2:J7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2.2 ↔ розд. 6 (вимога про 375 px, без ID)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній). 2.2 задає мінімальне вікно 1280×800, а вимога розділу 6 — коректний вигляд за ширини 375 px. Відсутній ID у вимозі розділу 6 — окремий дефект простежуваності, у цей рядок не входить.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>2.2: «мінімальна роздільна здатність вікна 1280×800». Розд. 6: «Інтерфейс коректно відображається за ширини вікна 375 пікселів».</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>У 2.2: «Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах; підтримувані розміри вікна — від 375 пікселів у ширину (мобільний вигляд інтерфейсу) і більше, основний настільний розмір — 1280×800.» (Мінімальну ширину 375 px узято з розділу 6 — потребує підтвердження замовником.)</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>F-30</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Єдиний пункт чек-листа: вимога здійсненна з погляду ресурсів і не залежить від систем, які продукт не контролює. Доставка до скриньки залежить від поштового провайдера одержувача.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>«гарантує його доставку до поштової скриньки користувача не довше ніж за 1 секунду незалежно від поштового провайдера одержувача».</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>«Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому сервісу не довше ніж за 1 секунду; час доставки до скриньки залежить від поштового провайдера одержувача і не гарантується.»</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Розділи 1–2 і 3. Простежуваність: у цих розділах дефектів немає (ID F-10…F-140 унікальні, крок 10); дефекти ID — у розділах 4–6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>F-90</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Практичний тест: немає критерію «пройдено / не пройдено». Слова-маркери «миттєво» (немає числа) і «без помилок» (не задано, що спостерігати).</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>«Натискання «Add to cart» додає товар у кошик у вказаній кількості миттєво і без помилок».</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>«Натискання «Add to cart» не довше ніж за 1 с додає товар у кошик у вказаній кількості (позиція з'являється на кроці «Cart»), повідомлення про помилку не виводиться; повторне додавання того самого товару збільшує його кількість у кошику.» (Значення 1 с — потребує підтвердження замовником.)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I10:J14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Розподіл розділів" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_horbonos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_korotka" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +111,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1124,4 +1129,858 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID/локатор</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Пункт чек-листа</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цитата</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Виправлення</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Хто знайшов</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Примітка</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Рядків</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>розд. 2.2 ↔ розд. 6, рядок 7, без ID</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>«Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах; мінімальна роздільна здатність вікна 1280×800» (2.2) суперечить «Інтерфейс коректно відображається за ширини вікна 375 пікселів … кнопками, придатними для натискання пальцем (не менше 44×44 пікселі)» (розд. 6). 2.2 обмежує продукт настільними ОС і шириною від 1280 пікселів, а розд. 6 вимагає мобільної ширини 375 пікселів і сенсорного керування.</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>2.2: «Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах, Chrome для Android 120 і новіші, Safari для iOS 17 і новіші; мінімальна ширина вікна — 375 пікселів.»</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>Версії мобільних браузерів — потребує підтвердження замовником. Пов'язано з рядком 14.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="K2">
+        <f>COUNTIF($C$2:$C$19,J2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>GUI-10</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>п. 1 — вимога містить повну інформацію</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>«…«Sign in» та перемикач мови інтерфейсу» — не вказано, які мови доступні і яка мова за замовчуванням (у 2.2: «Інтерфейс demo — англійською мовою»).</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>«…«Sign in» та перемикач мови інтерфейсу з варіантами DE, EL, EN, ES, FR, NL, TR; мова за замовчуванням — EN.»</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>Перелік мов звірено з demo 01.10.2026. Середня впевненість.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="K3">
+        <f>COUNTIF($C$2:$C$19,J3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>GUI-20 ↔ F-40</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>«Картки каталогу розміщуються сіткою у три колонки по 12 карток на сторінці» (GUI-20) суперечить «по 9 карток на сторінці» (F-40).</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>GUI-20: «Картки каталогу розміщуються сіткою у три колонки по 9 карток на сторінці (три ряди); …» (решта без змін).</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>9 карток — як у F-40 і в demo (перевірено 01.10.2026).</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="K4">
+        <f>COUNTIF($C$2:$C$19,J4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>GUI-30 ↔ BL-10, BL-40</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>«приймає значення від 0 до 100» (GUI-30) суперечить «qty — ціле число від 1 до 99 включно» (BL-10) і «встановлює нову кількість від 1 до 99 включно» (BL-40): інтерфейс дозволяє 0 і 100, які модуль відхиляє.</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>GUI-30: «Поле «Quantity» на сторінці товару — числове, з кнопками «−» і «+» ліворуч і праворуч; приймає цілі значення від 1 до 99 включно; значення за замовчуванням — 1.»</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="K5">
+        <f>COUNTIF($C$2:$C$19,J5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>F-120 ↔ GUI-40</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>«Покупець може додати товар до списку обраного кнопкою «Add to favourites» без входу в систему» (F-120) суперечить GUI-40: «якщо покупець не увійшов у систему, після натискання виводиться повідомлення «Unauthorized, can not add product to your favorite list», і товар до обраного не додається»; також 1.3 («Список товарів, збережених зареєстрованим покупцем») і 2.1 (обране — лише зареєстрованому покупцю).</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>F-120: «Зареєстрований покупець, який увійшов у систему, додає товар до списку обраного кнопкою «Add to favourites»; для неавторизованого користувача діє GUI-40. Список обраного доступний у кабінеті («My favorites»), де позицію можна видалити.»</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>крос — виправлення в F-120 (розд. 3); виявлено звіркою GUI-40 ↔ F-120.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="K6">
+        <f>COUNTIF($C$2:$C$19,J6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>GUI-50</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>«відображається біля відповідного поля або у верхній частині форми» — «або» дає два допустимі місця; очікуваний результат тест-кейсу неоднозначний, різні форми можуть поводитися по-різному.</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>«Повідомлення про помилку валідації поля форми відображається текстом безпосередньо під відповідним полем; форма, що містить помилки, не надсилається.»</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Місце виводу — потребує підтвердження замовником. Середня впевненість.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="K7">
+        <f>COUNTIF($C$2:$C$19,J7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>GUI-60 (два рядки)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — усі вимоги мають унікальний ідентифікатор</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Дві різні вимоги мають однаковий ID: «GUI-60 Форма входу містить поля «Email address» та «Password»…» і «GUI-60 Форма реєстрації містить поля у такому порядку…».</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Залишити GUI-60 за формою входу; формі реєстрації присвоїти вільний проміжний ID GUI-65 (між GUI-60 і GUI-70); решту ID не змінювати.</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="K8" s="11">
+        <f>SUM(K2:K7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>GUI-70</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>п. 1, 4 — вимога має одне значення й допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>«Порожній кошик відображає текстове повідомлення замість таблиці» — не вказано, яке саме повідомлення; тест-кейс не має очікуваного результату.</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>«Порожній кошик відображає замість таблиці текст «The cart is empty».»</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Текст повідомлення — потребує підтвердження замовником. Середня впевненість.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>GUI-80</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>єдиний пункт — технічні ресурси; залежність від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>«…у роздільній здатності не менше 8K (7680×4320 пікселів) без стиснення і завантажуються не довше ніж за 50 мс кожне за будь-якого з'єднання з Інтернетом» — нестиснене 8K-зображення ≈ 100 МБ; завантаження за 50 мс потребує ≈ 16 Гбіт/с, а швидкість з'єднання користувача продукт не контролює.</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>«Зображення товару на сторінці товару мають роздільну здатність не менше 1200×1200 пікселів, на картках каталогу — не менше 400×400 пікселів; за з'єднання 10 Мбіт/с зображення картки завантажується не довше ніж за 1 с.»</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Значення — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>GUI-100</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>немає критерію «пройдено / не пройдено»; слова-маркери</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>«Кольорова схема інтерфейсу є приємною і сучасною, а шрифти — легкими для читання на всіх сторінках» — «приємною», «сучасною», «легкими для читання» неможливо перевірити однозначно.</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>«На всіх сторінках контраст основного тексту до фону — не менше 4,5:1, розмір шрифту основного тексту — не менше 14 пікселів.»</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Значення — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>єдиний пункт — залежність від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>«…повністю завантажується не довше ніж за 0,1 с за будь-якого з'єднання з Інтернетом і на будь-якому пристрої» — час залежить від з'єднання й пристрою користувача; до того ж P-20 дозволяє відповідь API каталогу до 1 с, тож сторінка з даними API не завантажиться за 0,1 с.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>«Сторінка каталогу повністю завантажується не довше ніж за 3 с у 95 % вимірювань у Chrome 120 на настільному комп'ютері за з'єднання 10 Мбіт/с (20 вимірювань інструментом Lighthouse).»</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Значення — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>S-10</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>немає критерію «пройдено / не пройдено»; слово-маркер «надійно»</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>«Дані покупців надійно захищені, а система не містить вразливостей» — що спостерігати, невідомо; відсутність вразливостей неможливо довести тестом.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>«Паролі покупців зберігаються лише у вигляді хешу bcrypt; сторінки й API доступні лише через HTTPS (запит по HTTP перенаправляється на HTTPS); запит до даних покупця Б з токеном покупця А повертає код 403.»</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Перелік заходів — потребує підтвердження замовником. «Не містить вразливостей» порушує й здійсненність, але головний критерій — тестопридатність.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>U-10</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>немає критерію «пройдено / не пройдено»; слова-маркери «інтуїтивно», «зручно»</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>«Інтерфейс є інтуїтивно зрозумілим і зручним для всіх категорій користувачів».</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>«Новий користувач без інструкції знаходить товар пошуком, додає його в кошик і доходить до кроку «Payment» не довше ніж за 3 хв і не більше ніж з однією помилкою; перевірка на 5 учасниках, критерій — 4 з 5.»</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>Значення — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>розд. 6, рядок 7 (між U-20 і D-10), без ID</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — усі вимоги мають унікальний ідентифікатор</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>«Інтерфейс коректно відображається за ширини вікна 375 пікселів: без горизонтального прокручування, з доступним меню навігації та кнопками, придатними для натискання пальцем (не менше 44×44 пікселі)» — рядок вимоги без ідентифікатора.</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Присвоїти вільний ID U-30 (наступний у групі U, крок 10).</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Зміст рядка суперечить 2.2 — див. рядок 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>п. 3 — немає посилань на неіснуючі документи</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>«розділ про програму лояльності укладено згідно з «Регламентом програми лояльності ШопЛайн-ЛП-2025», розділ 4» — цього документа немає в 1.4 «Посилання».</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>«…розділ про програму лояльності описує правила BL-50 – BL-80 цієї специфікації (знижка за обсяг, вартість доставки, промокоди).»</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Якщо регламент існує — додати його до 1.4 (потребує підтвердження замовником).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>F-110 ↔ BL-60</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>«вартість доставки: 120 грн, а для замовлень від 2000 грн доставка безкоштовна» (F-110) суперечить «0.00 грн, якщо сума після знижки не менша за 1500 грн; інакше 120.00 грн» (BL-60): різний поріг (2000 / 1500) і різна база (сума замовлення / сума після знижки).</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>F-110: «…знижку за промокодом і вартість доставки, обчислену за BL-60.»</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>крос (розд. 3, 5). Правильний поріг — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>F-100</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>п. 3 (і п. 1) — немає посилань на неіснуюче</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>«Обмеження на кількість одиниць у рядку визначає вимога BL-25» — вимоги BL-25 у специфікації немає.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>«Обмеження на кількість одиниць у рядку (від 1 до 99) визначають вимоги BL-10, BL-20 і BL-40.»</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>крос (розд. 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>BL-30 ↔ BL-20</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>п. 1, 5 — вимоги унікальні й не перекриваються за змістом</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>BL-30 «Якщо в кошику вже є товар із таким самим артикулом, система не додає окремий рядок, а збільшує кількість у наявному рядку на вказане значення» повторює BL-20 «Повторне додавання позиції з тим самим sku не створює новий рядок, а збільшує кількість наявного рядка на qty».</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Залишити BL-20; BL-30 вилучити із записом у журналі змін (номер не перевикористовувати), посилання на BL-30 замінити на BL-20.</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>крос (розд. 5).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Розподіл розділів" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_horbonos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_korotka" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Розподіл розділів" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="audit_horbonos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="audit_korotka" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="audit_tymchak" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,1057 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID/локатор</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Пункт чек-листа</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цитата</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Виправлення</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Хто знайшов</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Примітка</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>Рядків</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>п. 1 — вимога містить повну інформацію</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>«обов'язковість полів позначено у формі зірочкою» — вимога не називає, які саме поля обов'язкові; тест-кейс для незаповненого поля неможливо скласти.</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>«… Обов'язкові поля: ім'я, прізвище, дата народження, країна, поштовий індекс, номер будинку, вулиця, місто, телефон, адреса електронної пошти, пароль; поле «область (штат)» необов'язкове; обов'язкові поля позначено у формі зірочкою.»</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="K2">
+        <f>COUNTIF($C$2:$C$25,J2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>п. 5 — описано реакції на помилки та виняткові ситуації</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>«Після успішної реєстрації система створює обліковий запис покупця і переходить на сторінку входу» — не описано реакцію на вже зареєстровану адресу електронної пошти.</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Додати до F-10: «Якщо адреса електронної пошти вже зареєстрована, обліковий запис не створюється, і система показує повідомлення «A customer with this email address already exists.»»</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>Текст повідомлення — Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="K3">
+        <f>COUNTIF($C$2:$C$25,J3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>F-20</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>«Після успішного входу система перенаправляє користувача на відповідну сторінку» — «відповідну» не визначено, очікуваний результат тесту неоднозначний.</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>«Після успішного входу система перенаправляє покупця на сторінку особистого кабінету «My account».»</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="K4">
+        <f>COUNTIF($C$2:$C$25,J4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>F-30</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>вимоги здійсненні з погляду наявних ресурсів; виконання не залежить від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>«гарантує його доставку до поштової скриньки користувача не довше ніж за 1 секунду незалежно від поштового провайдера одержувача» — доставка залежить від сторонніх поштових серверів, які продукт не контролює.</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>«Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому серверу ШопЛайн не пізніше ніж за 5 с; час доставки до скриньки одержувача залежить від його поштового провайдера і не гарантується.»</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Значення 5 с — Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="K5">
+        <f>COUNTIF($C$2:$C$25,J5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>F-40 ↔ GUI-20</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>F-40: «по 9 карток на сторінці»; GUI-20: «у три колонки по 12 карток на сторінці» — різна кількість карток на сторінці.</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>GUI-20: «Картки каталогу розміщуються сіткою у три колонки, по 9 карток на сторінці (відповідно до F-40); …»</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>крос (GUI-20 — розд. 4). Кількість 9 — Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="K6">
+        <f>COUNTIF($C$2:$C$25,J6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>F-50</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>«Кілька фільтрів поєднуються за правилом «І»» — незрозуміло, чи «І» діє між прапорцями одного виду (дві категорії одночасно дадуть порожній список) чи лише між різними видами фільтрів.</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>«Фільтри різних видів (категорія, бренд, діапазон ціни, «Eco-Friendly Products») поєднуються за правилом «І»; кілька позначених прапорців одного виду поєднуються за правилом «АБО».»</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="K7">
+        <f>COUNTIF($C$2:$C$25,J7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>F-50</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>практичний тест: тест-кейс з однозначним результатом «пройдено / не пройдено»</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>«система показує текстове повідомлення про відсутність товарів» — текст не задано, тож тест не може однозначно перевірити результат.</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>«… список карток порожній, а система показує повідомлення «There are no products found.»»</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Текст повідомлення — Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>F-60</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>«знайти товари, назви яких схожі на введений запит» — «схожі» допускає різні тлумачення (підрядок, початок слова, нечіткий пошук).</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>«Поле пошуку на головній сторінці знаходить товари, назви яких містять введений запит як підрядок без урахування регістру.»</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>F-90</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>практичний тест: тест-кейс з однозначним результатом «пройдено / не пройдено»</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>«додає товар у кошик у вказаній кількості миттєво і без помилок» — слова-маркери «миттєво», «без помилок»; немає числа й способу спостереження.</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>«Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с лічильник біля «Cart» у шапці збільшується на цю кількість і виводиться повідомлення «Product added to shopping cart.»; повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Значення 2 с і текст повідомлення — Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>F-100</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>п. 3 — немає посилань на неіснуючі документи</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>«Обмеження на кількість одиниць у рядку визначає вимога BL-25» — вимоги BL-25 у SRS немає.</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>«Обмеження на кількість одиниць у рядку (від 1 до 99) визначають вимоги BL-10, BL-20 і BL-40.»</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>F-110 ↔ BL-60</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>F-110: «вартість доставки: 120 грн, а для замовлень від 2000 грн доставка безкоштовна»; BL-60: «0.00 грн, якщо сума після знижки не менша за 1500 грн; інакше 120.00 грн» — різні пороги безкоштовної доставки.</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>F-110: «… вартість доставки визначається за BL-60: 0.00 грн, якщо сума після знижок не менша за 1500 грн, інакше 120.00 грн.»</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Поріг 1500 грн — Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>F-110 ↔ розд. 2.3, пункт 3</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>F-110: «Підсумок замовлення містить суму товарів, знижку за обсяг, знижку за промокодом і вартість доставки»; 2.3: «Модуль програми лояльності … в поточній версії ще не інтегрований в інтерфейс» — інтерфейс не може показувати знижки модуля, який у нього не інтегровано.</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>F-110: «Підсумок замовлення містить суму товарів і вартість доставки; знижка за обсяг і знижка за промокодом у версії 1.0 в інтерфейсі не відображаються (розд. 2.3).»</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>крос (розд. 2.3). Альтернатива — інтегрувати модуль і змінити 2.3; Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>F-120 ↔ GUI-40</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>F-120: «Покупець може додати товар до списку обраного кнопкою «Add to favourites» без входу в систему»; GUI-40: «якщо покупець не увійшов у систему … товар до обраного не додається»; розд. 2.1 відносить «обране» до функцій зареєстрованого покупця.</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>F-120: «Зареєстрований покупець, який увійшов у систему, може додати товар до списку обраного кнопкою «Add to favourites»; для неавторизованого покупця товар не додається (GUI-40). Список обраного доступний у кабінеті («My favorites»), де позицію можна видалити.»</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>крос (GUI-40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>F-140</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — обумовлено всі допустимі й недопустимі вхідні дані</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>«довжина повідомлення — не менше 50 символів. До звернення можна додати файл-вкладення» — не задано максимальну довжину повідомлення, допустимий формат і розмір вкладення та реакцію на недопустимий файл.</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>«… довжина повідомлення — від 50 до 250 символів. До звернення можна додати один файл формату .txt розміром до 500 КБ; для недопустимого файла звернення не надсилається, а біля поля виводиться повідомлення про помилку (GUI-50).»</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Межі довжини, формат і розмір файла — Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>BL-10</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — обумовлено всі допустимі й недопустимі вхідні дані</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>«Допустимі значення: qty — …; unitPrice — …; sku — непорожній рядок» — для параметра name допустимі значення не задано (null, порожній рядок).</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>«Допустимі значення: qty — ціле число від 1 до 99 включно; unitPrice — сума в гривнях, строго більша за 0; sku і name — непорожні рядки. …»</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>BL-30</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>п. 1 — вимоги унікальні й не повторюються</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>BL-30: «Якщо в кошику вже є товар із таким самим артикулом, система не додає окремий рядок, а збільшує кількість у наявному рядку» повторює BL-20: «Повторне додавання позиції з тим самим sku не створює новий рядок, а збільшує кількість наявного рядка».</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Вилучити BL-30 (ID залишається «діркою»); посилання на BL-30 замінити на BL-20.</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>BL-40</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — формат ID дозволяє розділяти вимогу без впливу на решту ID</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>BL-40 під одним ID описує чотири методи: «Cart.removeItem(sku) …; Cart.changeQty(sku, qty) …; Cart.subtotal() …; Cart.itemCount() …» — окремий юніт-тест не можна простежити до окремої вимоги.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>BL-40: «Cart.removeItem(sku) видаляє рядок; для відсутнього sku кидає NoSuchElementException.» BL-42: «Cart.changeQty(sku, qty) встановлює нову кількість від 1 до 99 включно (інакше IllegalArgumentException); для відсутнього sku кидає NoSuchElementException.» BL-44: «Cart.subtotal() повертає суму добутків «ціна × кількість» за всіма рядками, округлену до копійок (HALF_UP); для порожнього кошика — 0.00.» BL-46: «Cart.itemCount() повертає суму кількостей усіх рядків; для порожнього кошика — 0.»</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>BL-50</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>«при сумі від 2000 грн — 5 %, від 5000 грн — 10 %, від 10000 грн — 15 %» — діапазони перекриваються (сума 6000 грн одночасно «від 2000» і «від 5000»), межі не позначено як включні чи виключні.</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>«… обчислює знижку за обсяг: subtotal &lt; 2000 — 0 %; 2000 ≤ subtotal &lt; 5000 — 5 %; 5000 ≤ subtotal &lt; 10000 — 10 %; subtotal ≥ 10000 — 15 %; …»</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>BL-60</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>«shippingFee(subtotalAfterDiscount) … якщо сума після знижки не менша за 1500 грн» — не визначено, яку знижку віднімають: лише за обсягом (BL-50) чи також за промокодом (BL-80).</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>«… де subtotalAfterDiscount = subtotal − знижка за обсяг (BL-50) − знижка за промокодом (BL-80); повертає 0.00 грн, якщо subtotalAfterDiscount не менша за 1500 грн, інакше 120.00 грн. …»</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>BL-70</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>практичний тест: тест-кейс з однозначним результатом «пройдено / не пройдено»</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>«Результат містить ознаку придатності та причину відмови» — можливі причини відмови не перелічено, тож тест не може перевірити, що повернуто правильну причину.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>«… Причина відмови — одне зі значень: NOT_FOUND (код не існує), INVALID_FORMAT (довжина поза межами 6–10 символів), EXPIRED (дата закінчення раніша за today), ALREADY_USED (одноразовий код уже використано), INVALID_VALUE (значення поза допустимими межами); для придатного коду причина порожня.»</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>BL-80</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>вимоги здійсненні з погляду наявних ресурсів; виконання не залежить від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>«система перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх» — модуль не має доступу до даних сторонніх магазинів; до того ж за 2.3 бібліотека «без зовнішніх залежностей».</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>«Перед застосуванням одноразового коду метод перевіряє, що код не позначений як використаний у ШопЛайн; використаний код відхиляється (IllegalArgumentException із причиною відмови за BL-70).»</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>BL-70, BL-80 (немає вимоги)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — усі необхідні вимоги присутні</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>BL-70: фіксована сума «не перевищує subtotal», BL-50: знижка за обсяг — до 15 % від subtotal; правила сумісного застосування знижок немає, тож сума до оплати може бути від'ємною (subtotal 2000, знижка за обсяг 100, промокод 2000 → −100).</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Нова вимога BL-90: «Сума до оплати = subtotal − знижка за обсяг (BL-50) − знижка за промокодом (BL-80); якщо результат менший за 0.00, він дорівнює 0.00; до суми до оплати додається вартість доставки (BL-60).»</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>GUI-30 ↔ BL-10</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>GUI-30: «приймає значення від 0 до 100»; BL-10: «qty — ціле число від 1 до 99 включно».</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>GUI-30: «… приймає цілі значення від 1 до 99 включно; значення за замовчуванням — 1.»</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>крос (GUI-30 — розд. 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>GUI-60 (2 рядки)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>п. 2 — усі вимоги мають унікальний ідентифікатор</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Ідентифікатор GUI-60 присвоєно двом різним вимогам: «Форма входу містить поля …» і «Форма реєстрації містить поля у такому порядку …».</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Форму реєстрації позначити новим ID GUI-65; форма входу залишається GUI-60.</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>крос (розд. 4)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>«Після успішного входу система перенаправляє покупця на сторінку особистого кабінету «My account».»</t>
+          <t>«Після успішного входу система перенаправляє покупця на сторінку особистого кабінету (F-130).»</t>
         </is>
       </c>
       <c r="G4" s="12" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>«Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с лічильник біля «Cart» у шапці збільшується на цю кількість і виводиться повідомлення «Product added to shopping cart.»; повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
+          <t>«Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с після натискання виводиться повідомлення «Product added to shopping cart.»; повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Розподіл розділів" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_horbonos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_korotka" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_drepina" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +34,20 @@
     <font>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -49,7 +64,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -85,11 +100,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,6 +145,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1983,4 +2036,700 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>ID/локатор</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Пункт чек-листа</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Цитата</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Виправлення</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Хто знайшов</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>Рядків</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>GUI-20 ↔ F-40</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній)</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>«Картки каталогу розміщуються сіткою у три колонки по 12 карток на сторінці» — суперечить F-40 («по 9 карток на сторінці, з посторінковою навігацією»).</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>«Картки каталогу розміщуються сіткою у три колонки по 9 карток на сторінці; картка містить зображення, назву, шкалу класу CO2 і ціну; для відсутнього товару поверх зображення виводиться позначка "Out of stock".»</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="I2" s="17" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="J2" s="18">
+        <f>COUNTIF($C$2:$C$17,I2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>GUI-30 ↔ BL-10</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній)</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>«приймає значення від 0 до 100; значення за замовчуванням — 1» — суперечить BL-10 («qty — ціле число від 1 до 99 включно»). Поле дозволяє ввести 0 та 100, що призведе до невідповідності з модулем бізнес-логіки.</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>«Поле "Quantity" на сторінці товару числове, з кнопками "-" і "+" ліворуч і праворуч; приймає значення від 1 до 99 включно; значення за замовчуванням — 1.»</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="J3" s="18">
+        <f>COUNTIF($C$2:$C$17,I3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>F-120 ↔ GUI-40</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній)</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>«Покупець може додати товар до списку обраного кнопкою "Add to favourites" без входу в систему» — суперечить GUI-40 («якщо покупець не увійшов у систему... виводиться повідомлення "Unauthorized...", і товар до обраного не додається»), а також розділам 1.3 («Обране — список товарів, збережених зареєстрованим покупцем») та 2.1 (роль «Гість» не має обраного).</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Нова редакція F-120: «Покупець може додати товар до списку обраного кнопкою "Add to favourites" лише після входу в систему; список обраного доступний у кабінеті ("My favorites"), де позицію можна видалити (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="J4" s="18">
+        <f>COUNTIF($C$2:$C$17,I4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>GUI-60 (форма реєстрації)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>п. 2 (усі вимоги мають унікальний ідентифікатор)</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>«GUI-60 Форма реєстрації містить поля у такому порядку: First name, Last name...» — ідентифікатор GUI-60 продубльовано для двох різних вимог (форма входу та форма реєстрації).</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Присвоїти формі реєстрації унікальний ідентифікатор «GUI-65» (крок 5 між GUI-60 та GUI-70): «GUI-65 Форма реєстрації містить поля у такому порядку: First name, Last name, Date of Birth, Country, Postal code, House number, Street, City, State, Phone, Email address, Password; під полем пароля виводяться перелік правил для пароля та індикатор надійності...»</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="J5" s="18">
+        <f>COUNTIF($C$2:$C$17,I5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>GUI-80</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>п. 1 (вимоги здійсненні з погляду технічних ресурсів та фізичних обмежень мережі)</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>«у роздільній здатності не менше 8К (7680x4320 пікселів) без стиснення і завантажуються не довше ніж за 50 мс кожне за будь-якого з'єднання з Інтернетом» — фізично й технічно нездійсненно: нестиснене зображення такої роздільності важить десятки мегабайт і фізично не завантажиться за 50 мс через затримки мережі (RTT).</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>«Зображення товарів на картках каталогу і на сторінці товару оптимізуються для веб-середовища (роздільна здатність до 800x800 пікселів, формат WebP або JPEG, розмір до 250 КБ) і завантажуються не довше ніж за 1,5 с при швидкості підключення від 10 Мбіт/с (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="J6" s="18">
+        <f>COUNTIF($C$2:$C$17,I6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>GUI-100</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>п. 1 (бракує числа або об'єктивного способу спостереження; суб'єктивні оцінки)</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>«Кольорова схема інтерфейсу є приємною і сучасною, а шрифти — легкими для читання на всіх сторінках» — суб'єктивні неконкретні маркери («приємною», «сучасною», «легкими для читання»), результат яких неможливо об'єктивно перевірити як Pass/Fail.</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>«Кольорова схема інтерфейсу забезпечує коефіцієнт контрастності тексту щодо фону не менше 4.5:1 для основного тексту та не менше 3:1 для великих елементів за стандартом WCAG 2.1 AA; розмір основного шрифту становить не менше 14px (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="J7" s="18">
+        <f>COUNTIF($C$2:$C$17,I7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>BL-10</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>п. 4 (допускає єдину інтерпретацію; правило перевірки межі до чи після округлення)</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>«unitPrice — сума в гривнях, строго більша за 0; sku — непорожній рядок... Ціна зберігається з округленням до копійок (HALF_UP).» — не визначено однозначно: перевірка умови «unitPrice &gt; 0» виконується ДО чи ПІСЛЯ округлення за правилом HALF_UP (наприклад, значення 0.004 строго більше 0, але після округлення HALF_UP перетворюється на 0.00 грн).</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>«Cart.addItem(sku, name, unitPrice, qty) додає позицію до кошика. Допустимі значення: qty — ціле число від 1 до 99 включно; unitPrice — сума в гривнях, яка після обов'язкового округлення за правилом HALF_UP до 2 знаків після коми є строго більшою за 0.00 грн (перевірка "ціна &gt; 0" виконується після нормалізації/округлення); sku — непорожній рядок. За порушення будь-якої умови метод кидає IllegalArgumentException, а вміст кошика не змінюється.»</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="J8" s="20">
+        <f>SUM(J2:J7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>BL-30</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>п. 1 (вимоги унікальні й не повторюються за змістом)</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>«Якщо в кошику вже є товар із таким самим артикулом, система не додає окремий рядок, а збільшує кількість у наявному рядку на вказане значення.» — вимога повністю дублює бізнес-правило повторного додавання з BL-20.</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Вилучити вимогу BL-30 як надлишковий дублікат BL-20. Залишити ідентифікатор BL-30 як вільний («дірка» в нумерації без зсуву інших ID згідно з правилами трасування).</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>GUI-50</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>п. 1, 4 (допускає єдину інтерпретацію; частка «або» дає два різні очікувані результати)</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>«Повідомлення про помилку валідації поля форми відображається біля відповідного поля або у верхній частині форми; форма, що містить помилки, не надсилається.» — неоднозначність у розташуванні: частка «або» допускає дві взаємовиключні поведінки інтерфейсу без визначення конкретного правила, коли і де саме показується повідомлення.</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>«Повідомлення про помилку валідації поля форми відображається безпосередньо під відповідним полем введення червоним кольором із текстовою міткою; форма, що містить хоча б одне невалідне поле, блокує відправку (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>BL-60 ↔ F-110</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>п. 2 (вимоги не суперечать одна одній)</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>«DiscountCalculator.shippingFee (subtotalAfterDiscount) повертає вартість доставки: 0.00 грн, якщо сума після знижки не менша за 1500 грн; інакше 120.00 грн.» — прямо суперечить вимозі F-110 («а для замовлень від 2000 грн доставка безкоштовна»).</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Нова редакція F-110: «Оформлення замовлення складається з чотирьох кроків: «Cart» → «Sign in» → «Billing Address» → «Payment». Неавторизований покупець на кроці 2 входить або реєструється; на кроці 3 підтверджує адресу доставки (вулиця, місто, область, країна, поштовий індекс); на кроці 4 обирає спосіб оплати (банківський переказ, оплата при отриманні, кредитна картка, «купити зараз заплатити пізніше», подарункова картка) і підтверджує замовлення. Підсумок замовлення містить суму товарів, знижку за обсяг, знижку за промокодом і вартість доставки: 120 грн; якщо сума замовлення після знижки за обсяг становить не менше 1500 грн, доставка безкоштовна (потребує підтвердження замовником). Після підтвердження система показує повідомлення з номером рахунку-інвойсу.»</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>BL-80</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>п. 1 (виконання не залежить від систем, які продукт не контролює)</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>«Перед застосуванням одноразового коду система перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх, і в такому разі відхиляє його.» — технічно й юридично нездійсненно (модуль не має доступу до сторонніх систем).</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>«Перед застосуванням одноразового коду PromoCodeValidator перевіряє ознаку одноразовості та ознаку використання переданого запису PromoCode; якщо код уже позначено як використаний, метод відхиляє його та кидає IllegalArgumentException.»</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>п. 1 (здійсненність з погляду фізичних обмежень передачі даних у мережі)</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>«Сторінка каталогу повністю завантажується не довше ніж за 0,1 с за будь-якого з'єднання з Інтернетом і на будь-якому пристрої.» — фізично нездійсненно (0,1 с менше або на рівні мінімальної затримки RTT мобільних мереж лише на встановлення з'єднання).</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>«Час повного завантаження сторінки каталогу на настільних пристроях не перевищує 2,0 с при швидкості широкосмугового інтернет-з'єднання від 15 Мбіт/с; показник First Contentful Paint (FCP) становить не більше 1,0 с (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>S-10</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>п. 1 (бракує способу спостереження, критерію Pass/Fail; неконкретне твердження)</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>«Дані покупців надійно захищені, а система не містить вразливостей.» — розпливчасті нетестопридатні твердження («надійно захищені», «не містить вразливостей»).</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>«Усі канали передачі персональних даних покупців захищені протоколом HTTPS (TLS 1.3); паролі зберігаються в базі даних виключно у хешованому вигляді (алгоритм bcrypt із сіллю); за результатами звіту сканування безпеки на локальному тестовому стенді розробників (на публічному demo сканування не проводиться) у релізі відсутні вразливості категорій Critical та High (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>U-10</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>п. 1 (бракує числа або вимірюваного значення; слова-маркери нетестопридатності)</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>«Інтерфейс є інтуїтивно зрозумілим і зручним для всіх категорій користувачів.» — пряме використання заборонених суб'єктивних слів-маркерів «інтуїтивно зрозумілий» та «зручний».</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>«Новий користувач без попереднього інструктажу успішно проходить наскрізний чекаут не довше ніж за 3 хвилини; показник Task Success Rate становить не менше 90% при вибірці з 10 респондентів (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Розділ 6, між U-20 та D-10</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>п. 2 (усі вимоги мають унікальний ідентифікатор; вимога не має ID)</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>«Інтерфейс коректно відображається за ширини вікна 375 пікселів: без горизонтального прокручування, з доступним меню навігації та кнопками, придатними для натискання пальцем (не менше 44×44 пікселі).» — вимога не має ідентифікатора в колонці ID.</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Присвоїти вимозі унікальний ідентифікатор «U-30» (крок 10 після U-20 у групі Usability): «U-30 Інтерфейс коректно відображається за ширини вікна 375 пікселів: без горизонтального прокручування, з доступним меню навігації та кнопками, придатними для натискання пальцем (не менше 44×44 пікселі).»</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>п. 3 (немає посилань на неіснуючі документи або регламенти)</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>«розділ про програму лояльності укладено згідно з "Регламентом програми лояльності ШопЛайн-ЛП-2025", розділ 4.» — посилання на неіснуючий зовнішній документ (у розділі 1.4 він відсутній).</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>«Посібник користувача покриває реєстрацію, пошук, оформлення замовлення і роботу з кабінетом; розділ про програму лояльності укладено згідно з вимогами розділу 5 цієї специфікації.»</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -12,8 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_korotka" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_drepina" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_tymchak" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реєстр" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Реєстр'!$A$1:$J$37</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -64,8 +71,13 @@
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -115,11 +127,17 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -171,10 +189,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+          <bgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -3786,4 +3824,1982 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>ID/локатор</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>Пункт чек-листа</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>Опис дефекту (цитата)</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>Пропозиція виправлення</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>Хто знайшов</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>Джерела</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>Примітка</t>
+        </is>
+      </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>Критерій</t>
+        </is>
+      </c>
+      <c r="M1" s="11" t="inlineStr">
+        <is>
+          <t>Рядків</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>2.2 ↔ розд. 6 (вимога про 375 px, без ID)</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>«Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах; мінімальна роздільна здатність вікна 1280×800» (2.2) суперечить «Інтерфейс коректно відображається за ширини вікна 375 пікселів … кнопками, придатними для натискання пальцем (не менше 44×44 пікселі)» (розд. 6). 2.2 обмежує продукт настільними ОС і шириною від 1280 пікселів, а розд. 6 вимагає мобільної ширини 375 пікселів і сенсорного керування.</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Горбонос О. (СМ): У 2.2: «Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах; підтримувані розміри вікна — від 375 пікселів у ширину (мобільний вигляд інтерфейсу) і більше, основний настільний розмір — 1280×800.» (Мінімальну ширину 375 px узято з розділу 6 — потребує підтвердження замовником.)
+Варіант Коротка К. (КТ): 2.2: «Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах, Chrome для Android 120 і новіші, Safari для iOS 17 і новіші; мінімальна ширина вікна — 375 пікселів.»</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I2" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №8; audit_korotka №1</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>Відсутність ID у вимозі розд. 6 — окремий рядок (див. «розд. 6, між U-20 і D-10»). Варіанти виправлення різняться (мобільні браузери) — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="L2" s="23" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="M2" s="23">
+        <f>COUNTIF($C$2:$C$37,L2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>п. 1 — вимога містить повну інформацію</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>«обов'язковість полів позначено у формі зірочкою» — вимога не називає, які саме поля обов'язкові; тест-кейс для незаповненого поля неможливо скласти.</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>«… Обов'язкові поля: ім'я, прізвище, дата народження, країна, поштовий індекс, номер будинку, вулиця, місто, телефон, адреса електронної пошти, пароль; поле «область (штат)» необов'язкове; обов'язкові поля позначено у формі зірочкою.»</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №1</t>
+        </is>
+      </c>
+      <c r="J3" s="22" t="inlineStr">
+        <is>
+          <t>Інший дефект F-10 (зайнята e-mail) — окремий рядок. Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="M3" s="23">
+        <f>COUNTIF($C$2:$C$37,L3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>п. 5 — описано реакції на помилки та виняткові ситуації</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>«Після успішної реєстрації система створює обліковий запис покупця і переходить на сторінку входу» — не описано реакцію на вже зареєстровану адресу електронної пошти.</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Додати до F-10: «Якщо адреса електронної пошти вже зареєстрована, обліковий запис не створюється, і система показує повідомлення «A customer with this email address already exists.»»</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №2</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>Текст повідомлення — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="L4" s="23" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="M4" s="23">
+        <f>COUNTIF($C$2:$C$37,L4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>F-20</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — вимога чітка і зрозуміла; п. 4 — допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>«Після успішного входу система перенаправляє користувача на відповідну сторінку» — «відповідну» не визначено, очікуваний результат тесту неоднозначний.</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Горбонос О. (СМ): «Після успішного входу система перенаправляє покупця на сторінку особистого кабінету (/account); якщо вхід виконано на кроці «Sign in» оформлення замовлення (F-110) — на крок «Billing Address».»
+Варіант Тимчак А. (ТА): «Після успішного входу система перенаправляє покупця на сторінку особистого кабінету (F-130).»</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №1; audit_tymchak №3</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>Обидва варіанти ведуть у кабінет; варіант Горбонос додатково описує вхід на кроці «Sign in» (F-110).</t>
+        </is>
+      </c>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="M5" s="23">
+        <f>COUNTIF($C$2:$C$37,L5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>F-30</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>вимоги здійсненні з погляду наявних ресурсів; виконання не залежить від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>«гарантує його доставку до поштової скриньки користувача не довше ніж за 1 секунду незалежно від поштового провайдера одержувача» — доставка залежить від сторонніх поштових серверів, які продукт не контролює.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Горбонос О. (СМ): «Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому сервісу не довше ніж за 1 секунду; час доставки до скриньки залежить від поштового провайдера одержувача і не гарантується.»
+Варіант Тимчак А. (ТА): «Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому серверу ШопЛайн не пізніше ніж за 5 с; час доставки до скриньки одержувача залежить від його поштового провайдера і не гарантується.»</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №9; audit_tymchak №4</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти різняться лише часом передачі листа (1 с / 5 с) — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="M6" s="23">
+        <f>COUNTIF($C$2:$C$37,L6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>F-40 ↔ GUI-20</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>«Картки каталогу розміщуються сіткою у три колонки по 12 карток на сторінці» (GUI-20) суперечить «по 9 карток на сторінці» (F-40).</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>У GUI-20: «Картки каталогу розміщуються сіткою у три колонки по 9 карток на сторінці; картка містить зображення, назву, шкалу класу CO2 і ціну; для відсутнього товару поверх зображення виводиться позначка «Out of stock».»</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №7; audit_korotka №3; audit_drepina №1; audit_tymchak №5</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>Усі четверо пропонують виправити GUI-20 на 9 карток (як у F-40 і в demo).</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="M7" s="23">
+        <f>COUNTIF($C$2:$C$37,L7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>F-50</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>«Кілька фільтрів поєднуються за правилом «І»» — незрозуміло, чи «І» діє між прапорцями одного виду (дві категорії одночасно дадуть порожній список) чи лише між різними видами фільтрів.</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>«Фільтри різних видів (категорія, бренд, діапазон ціни, «Eco-Friendly Products») поєднуються за правилом «І»; кілька позначених прапорців одного виду поєднуються за правилом «АБО».»</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №6</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="M8" s="23">
+        <f>SUM(M2:M7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>F-50</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>практичний тест: тест-кейс з однозначним результатом «пройдено / не пройдено»</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>«система показує текстове повідомлення про відсутність товарів» — текст не задано, тож тест не може однозначно перевірити результат.</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>«… список карток порожній, а система показує повідомлення «There are no products found.»»</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>спірне</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №7</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>Класифікація: аналогічний дефект GUI-70 (текст повідомлення не задано) віднесено до однозначності — узгодити один критерій для обох рядків.</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>F-60</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>«знайти товари, назви яких схожі на введений запит» — «схожі» допускає різні тлумачення (підрядок, початок слова, нечіткий пошук).</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>«Поле пошуку на головній сторінці дозволяє знайти товари, назви яких містять введений запит (без урахування регістру літер).» (Правило звірено з demo: запит «PLI» повертає «Pliers», «Combination Pliers» та інші.)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №2; audit_tymchak №8</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення збігаються (підрядок, без урахування регістру).</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>Статус «спірне»</t>
+        </is>
+      </c>
+      <c r="M10" s="23">
+        <f>COUNTIF($H$2:$H$37,"спірне")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>F-90</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>практичний тест: тест-кейс з однозначним результатом «пройдено / не пройдено»</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>«додає товар у кошик у вказаній кількості миттєво і без помилок» — слова-маркери «миттєво», «без помилок»; немає числа й способу спостереження.</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Горбонос О. (СМ): «Натискання «Add to cart» не довше ніж за 1 с додає товар у кошик у вказаній кількості (позиція з'являється на кроці «Cart»), повідомлення про помилку не виводиться; повторне додавання того самого товару збільшує його кількість у кошику.» (Значення 1 с — потребує підтвердження замовником.)
+Варіант Тимчак А. (ТА): «Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с після натискання виводиться повідомлення «Product added to shopping cart.»; повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №10; audit_tymchak №9</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти різняться часом (1 с / 2 с) і способом спостереження — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>Рядків в аркушах аудиту</t>
+        </is>
+      </c>
+      <c r="M11" s="23" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>F-100</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>п. 3 — немає посилань на неіснуючі документи</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>«Обмеження на кількість одиниць у рядку визначає вимога BL-25» — вимоги BL-25 у специфікації немає.</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Коротка К. (КТ), Тимчак А. (ТА): «Обмеження на кількість одиниць у рядку (від 1 до 99) визначають вимоги BL-10, BL-20 і BL-40.»
+Варіант Горбонос О. (СМ): «Обмеження на кількість одиниць у рядку (ціле число від 1 до 99 включно) визначає вимога BL-40.»</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №3; audit_korotka №17; audit_tymchak №10</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>F-110 ↔ BL-60</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>«вартість доставки: 120 грн, а для замовлень від 2000 грн доставка безкоштовна» (F-110) суперечить «0.00 грн, якщо сума після знижки не менша за 1500 грн; інакше 120.00 грн» (BL-60): різний поріг (2000 / 1500) і різна база (сума замовлення / сума після знижки).</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Горбонос О. (СМ), Дрєпіна А. (ІТ): У F-110: «… вартість доставки: 120 грн; якщо сума замовлення після знижки за обсяг становить не менше 1500 грн, доставка безкоштовна.» (Поріг 1500 грн узято з BL-60 — потребує підтвердження замовником.)
+Варіант Тимчак А. (ТА), Коротка К. (КТ): F-110: «… вартість доставки визначається за BL-60: 0.00 грн, якщо сума після знижок не менша за 1500 грн, інакше 120.00 грн.»</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №5; audit_korotka №16; audit_drepina №10; audit_tymchak №11</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти різняться базою порогу: сума після знижки за обсяг (Горбонос, Дрєпіна) чи після всіх знижок (Тимчак, Коротка) — пов'язано з рядком BL-60 (однозначність). Поріг — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>Чернетка SCRUM-53. Рядки впорядковано за порядком SRS (2.2 → F → GUI → P/S/U/D → BL). Однакові дефекти (той самий ID, критерій, суть) зведено в один рядок з усіма авторами; коли виправлення різняться, наведено всі варіанти з авторами. «спірне» — розбіжність у класифікації або сумнівний рядок; вирішення — поза цією задачею.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>F-110 ↔ розд. 2.3, пункт 3</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>F-110: «Підсумок замовлення містить суму товарів, знижку за обсяг, знижку за промокодом і вартість доставки»; 2.3: «Модуль програми лояльності … в поточній версії ще не інтегрований в інтерфейс» — інтерфейс не може показувати знижки модуля, який у нього не інтегровано.</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>F-110: «Підсумок замовлення містить суму товарів і вартість доставки; знижка за обсяг і знижка за промокодом у версії 1.0 в інтерфейсі не відображаються (розд. 2.3).»</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>спірне</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №12</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Сумнівний: інші аудитори розділу 3 цього не позначили; виправлення конфліктує з варіантами виправлення рядка F-110 ↔ BL-60, які залишають знижки в підсумку. Альтернатива — інтегрувати модуль і змінити 2.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>F-120 ↔ GUI-40</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>«Покупець може додати товар до списку обраного кнопкою «Add to favourites» без входу в систему» (F-120) суперечить GUI-40: «якщо покупець не увійшов у систему, після натискання виводиться повідомлення «Unauthorized, can not add product to your favorite list», і товар до обраного не додається»; також 1.3 («Список товарів, збережених зареєстрованим покупцем») і 2.1 (обране — лише зареєстрованому покупцю).</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>F-120: «Зареєстрований покупець, який увійшов у систему, може додати товар до списку обраного кнопкою «Add to favourites»; для неавторизованого покупця товар не додається (GUI-40). Список обраного доступний у кабінеті («My favorites»), де позицію можна видалити.»</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №6; audit_korotka №5; audit_drepina №3; audit_tymchak №13</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення всіх чотирьох збігаються за змістом (обране — лише після входу; правиться F-120).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>F-140</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 — обумовлено всі допустимі й недопустимі вхідні дані; п. 5 — реакція на помилки</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>«довжина повідомлення — не менше 50 символів. До звернення можна додати файл-вкладення» — не задано максимальну довжину повідомлення, допустимий формат і розмір вкладення та реакцію на недопустимий файл.</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Горбонос О. (СМ): «До звернення можна додати один файл-вкладення розміром до 5 МБ у форматі PDF, PNG, JPG або TXT; для файлу, що не відповідає цим умовам, система показує повідомлення про недопустимий файл біля поля вкладення і не надсилає звернення (GUI-50).» (Формати й межа 5 МБ — потребує підтвердження замовником.)
+Варіант Тимчак А. (ТА): «… довжина повідомлення — від 50 до 250 символів. До звернення можна додати один файл формату .txt розміром до 500 КБ; для недопустимого файла звернення не надсилається, а біля поля виводиться повідомлення про помилку (GUI-50).»</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>audit_horbonos №4; audit_tymchak №14</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти різняться форматами й розміром файла (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ); максимальну довжину повідомлення пропонує лише Тимчак. Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>GUI-10</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>п. 1 — вимога містить повну інформацію</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>«…«Sign in» та перемикач мови інтерфейсу» — не вказано, які мови доступні і яка мова за замовчуванням (у 2.2: «Інтерфейс demo — англійською мовою»).</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>«…«Sign in» та перемикач мови інтерфейсу з варіантами DE, EL, EN, ES, FR, NL, TR; мова за замовчуванням — EN.»</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>спірне</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №2</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>Сумнівний: автор вказав середню впевненість; другий аудитор розділу 4 (Дрєпіна) не знайшов. Перелік мов звірено з demo 01.10.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>GUI-30 ↔ BL-10, BL-40</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Несуперечливість</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — вимоги не суперечать одна одній</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>«приймає значення від 0 до 100» (GUI-30) суперечить «qty — ціле число від 1 до 99 включно» (BL-10) і «встановлює нову кількість від 1 до 99 включно» (BL-40): інтерфейс дозволяє 0 і 100, які модуль відхиляє.</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>GUI-30: «Поле «Quantity» на сторінці товару — числове, з кнопками «−» і «+» ліворуч і праворуч; приймає цілі значення від 1 до 99 включно; значення за замовчуванням — 1.»</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №4; audit_drepina №2; audit_tymchak №23</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення всіх трьох збігаються (1–99, за замовчуванням 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>GUI-50</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>п. 1, 4 — вимога має одне значення й допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>«відображається біля відповідного поля або у верхній частині форми» — «або» дає два допустимі місця; очікуваний результат тест-кейсу неоднозначний, різні форми можуть поводитися по-різному.</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>«Повідомлення про помилку валідації поля форми відображається текстом безпосередньо під відповідним полем; форма, що містить помилки, не надсилається.»</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №6; audit_drepina №9</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення збігаються (під полем); Дрєпіна додатково пропонує червоний колір. Місце виводу — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>GUI-60 (два рядки)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — усі вимоги мають унікальний ідентифікатор</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>Дві різні вимоги мають однаковий ID: «GUI-60 Форма входу містить поля «Email address» та «Password»…» і «GUI-60 Форма реєстрації містить поля у такому порядку…».</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Залишити GUI-60 за формою входу; формі реєстрації присвоїти вільний проміжний ID GUI-65 (між GUI-60 і GUI-70); решту ID не змінювати.</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №7; audit_drepina №4; audit_tymchak №24</t>
+        </is>
+      </c>
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>Усі троє пропонують GUI-65 для форми реєстрації.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>GUI-70</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>п. 1, 4 — вимога має одне значення й допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>«Порожній кошик відображає текстове повідомлення замість таблиці» — не вказано, яке саме повідомлення; тест-кейс не має очікуваного результату.</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>«Порожній кошик відображає замість таблиці текст «The cart is empty».»</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>спірне</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №8</t>
+        </is>
+      </c>
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>Сумнівний: автор вказав середню впевненість; другий аудитор розділу 4 (Дрєпіна) не знайшов. Класифікація: аналогічний дефект F-50 віднесено до тестопридатності. Текст — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>GUI-80</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>єдиний пункт — технічні ресурси; залежність від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>«…у роздільній здатності не менше 8K (7680×4320 пікселів) без стиснення і завантажуються не довше ніж за 50 мс кожне за будь-якого з'єднання з Інтернетом» — нестиснене 8K-зображення ≈ 100 МБ; завантаження за 50 мс потребує ≈ 16 Гбіт/с, а швидкість з'єднання користувача продукт не контролює.</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Коротка К. (КТ): «Зображення товару на сторінці товару мають роздільну здатність не менше 1200×1200 пікселів, на картках каталогу — не менше 400×400 пікселів; за з'єднання 10 Мбіт/с зображення картки завантажується не довше ніж за 1 с.»
+Варіант Дрєпіна А. (ІТ): «Зображення товарів на картках каталогу і на сторінці товару оптимізуються для веб-середовища (роздільна здатність до 800x800 пікселів, формат WebP або JPEG, розмір до 250 КБ) і завантажуються не довше ніж за 1,5 с при швидкості підключення від 10 Мбіт/с (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №9; audit_drepina №5</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти суперечать один одному (не менше 1200×1200 / до 800×800) — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>GUI-100</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>немає критерію «пройдено / не пройдено»; слова-маркери</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>«Кольорова схема інтерфейсу є приємною і сучасною, а шрифти — легкими для читання на всіх сторінках» — «приємною», «сучасною», «легкими для читання» неможливо перевірити однозначно.</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>«Кольорова схема інтерфейсу забезпечує коефіцієнт контрастності тексту щодо фону не менше 4.5:1 для основного тексту та не менше 3:1 для великих елементів за стандартом WCAG 2.1 AA; розмір основного шрифту становить не менше 14px (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №10; audit_drepina №6</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення сумісні (4,5:1, 14 px); варіант Дрєпіної повніший (3:1 для великих елементів, WCAG 2.1 AA). Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>P-10</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>єдиний пункт — залежність від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>«…повністю завантажується не довше ніж за 0,1 с за будь-якого з'єднання з Інтернетом і на будь-якому пристрої» — час залежить від з'єднання й пристрою користувача; до того ж P-20 дозволяє відповідь API каталогу до 1 с, тож сторінка з даними API не завантажиться за 0,1 с.</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Коротка К. (КТ): «Сторінка каталогу повністю завантажується не довше ніж за 3 с у 95 % вимірювань у Chrome 120 на настільному комп'ютері за з'єднання 10 Мбіт/с (20 вимірювань інструментом Lighthouse).»
+Варіант Дрєпіна А. (ІТ): «Час повного завантаження сторінки каталогу на настільних пристроях не перевищує 2,0 с при швидкості широкосмугового інтернет-з'єднання від 15 Мбіт/с; показник First Contentful Paint (FCP) становить не більше 1,0 с (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №11; audit_drepina №12</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти різняться значеннями (3 с у 95 % при 10 Мбіт/с / 2 с і FCP 1 с при 15 Мбіт/с) — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>S-10</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>немає критерію «пройдено / не пройдено»; слово-маркер «надійно»</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>«Дані покупців надійно захищені, а система не містить вразливостей» — що спостерігати, невідомо; відсутність вразливостей неможливо довести тестом.</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Коротка К. (КТ): «Паролі покупців зберігаються лише у вигляді хешу bcrypt; сторінки й API доступні лише через HTTPS (запит по HTTP перенаправляється на HTTPS); запит до даних покупця Б з токеном покупця А повертає код 403.»
+Варіант Дрєпіна А. (ІТ): «Усі канали передачі персональних даних покупців захищені протоколом HTTPS (TLS 1.3); паролі зберігаються в базі даних виключно у хешованому вигляді (алгоритм bcrypt із сіллю); за результатами звіту сканування безпеки на локальному тестовому стенді розробників (на публічному demo сканування не проводиться) у релізі відсутні вразливості категорій Critical та High (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №12; audit_drepina №13</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти частково перетинаються (bcrypt, HTTPS) і можуть бути об'єднані. Коротка: «не містить вразливостей» порушує й здійсненність, головний критерій — тестопридатність. Перелік заходів — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>U-10</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>немає критерію «пройдено / не пройдено»; слова-маркери «інтуїтивно», «зручно»</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>«Інтерфейс є інтуїтивно зрозумілим і зручним для всіх категорій користувачів».</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>Варіант Коротка К. (КТ): «Новий користувач без інструкції знаходить товар пошуком, додає його в кошик і доходить до кроку «Payment» не довше ніж за 3 хв і не більше ніж з однією помилкою; перевірка на 5 учасниках, критерій — 4 з 5.»
+Варіант Дрєпіна А. (ІТ): «Новий користувач без попереднього інструктажу успішно проходить наскрізний чекаут не довше ніж за 3 хвилини; показник Task Success Rate становить не менше 90% при вибірці з 10 респондентів (потребує підтвердження замовником).»</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №13; audit_drepina №14</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти різняться методикою (4 з 5 учасників / 90 % з 10 респондентів) — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>розд. 6, між U-20 і D-10 (без ID)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — усі вимоги мають унікальний ідентифікатор</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>«Інтерфейс коректно відображається за ширини вікна 375 пікселів: без горизонтального прокручування, з доступним меню навігації та кнопками, придатними для натискання пальцем (не менше 44×44 пікселі)» — рядок вимоги без ідентифікатора.</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>Присвоїти вільний ID U-30 (наступний у групі U, крок 10).</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №14; audit_drepina №15</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>Обидва пропонують U-30. Зміст рядка суперечить 2.2 — див. рядок «2.2 ↔ розд. 6».</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>п. 3 — немає посилань на неіснуючі документи</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>«розділ про програму лояльності укладено згідно з «Регламентом програми лояльності ШопЛайн-ЛП-2025», розділ 4» — цього документа немає в 1.4 «Посилання».</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>«…розділ про програму лояльності описує правила BL-50 – BL-80 цієї специфікації (знижка за обсяг, вартість доставки, промокоди).»</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №15; audit_drepina №16</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення збігаються за змістом (посилатися на розділ 5 / BL-50 – BL-80). Якщо регламент існує — додати його до 1.4 (потребує підтвердження замовником).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>BL-10</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 (допускає єдину інтерпретацію; правило перевірки межі до чи після округлення)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>«unitPrice — сума в гривнях, строго більша за 0; sku — непорожній рядок... Ціна зберігається з округленням до копійок (HALF_UP).» — не визначено однозначно: перевірка умови «unitPrice &gt; 0» виконується ДО чи ПІСЛЯ округлення за правилом HALF_UP (наприклад, значення 0.004 строго більше 0, але після округлення HALF_UP перетворюється на 0.00 грн).</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>«Cart.addItem(sku, name, unitPrice, qty) додає позицію до кошика. Допустимі значення: qty — ціле число від 1 до 99 включно; unitPrice — сума в гривнях, яка після обов'язкового округлення за правилом HALF_UP до 2 знаків після коми є строго більшою за 0.00 грн (перевірка "ціна &gt; 0" виконується після нормалізації/округлення); sku — непорожній рядок. За порушення будь-якої умови метод кидає IllegalArgumentException, а вміст кошика не змінюється.»</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>audit_drepina №7</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>Інший дефект BL-10 (параметр name) — окремий рядок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>BL-10</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 — обумовлено всі допустимі й недопустимі вхідні дані</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>«Допустимі значення: qty — …; unitPrice — …; sku — непорожній рядок» — для параметра name допустимі значення не задано (null, порожній рядок).</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>«Допустимі значення: qty — ціле число від 1 до 99 включно; unitPrice — сума в гривнях, строго більша за 0; sku і name — непорожні рядки. …»</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №15</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>BL-30 ↔ BL-20</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>п. 1 — вимоги унікальні й не повторюються за змістом</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>BL-30 «Якщо в кошику вже є товар із таким самим артикулом, система не додає окремий рядок, а збільшує кількість у наявному рядку на вказане значення» повторює BL-20 «Повторне додавання позиції з тим самим sku не створює новий рядок, а збільшує кількість наявного рядка на qty».</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Залишити BL-20; BL-30 вилучити із записом у журналі змін (номер не перевикористовувати), посилання на BL-30 замінити на BL-20.</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>audit_korotka №18; audit_drepina №8; audit_tymchak №16</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>Усі троє пропонують вилучити BL-30, не перевикористовуючи номер.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>BL-40</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Простежуваність</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 — формат ID дозволяє розділяти вимогу без впливу на решту ID</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>BL-40 під одним ID описує чотири методи: «Cart.removeItem(sku) …; Cart.changeQty(sku, qty) …; Cart.subtotal() …; Cart.itemCount() …» — окремий юніт-тест не можна простежити до окремої вимоги.</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>BL-40: «Cart.removeItem(sku) видаляє рядок; для відсутнього sku кидає NoSuchElementException.» BL-42: «Cart.changeQty(sku, qty) встановлює нову кількість від 1 до 99 включно (інакше IllegalArgumentException); для відсутнього sku кидає NoSuchElementException.» BL-44: «Cart.subtotal() повертає суму добутків «ціна × кількість» за всіма рядками, округлену до копійок (HALF_UP); для порожнього кошика — 0.00.» BL-46: «Cart.itemCount() повертає суму кількостей усіх рядків; для порожнього кошика — 0.»</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>спірне</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №17</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>Класифікація: п. 4 перевіряє формат ID, а не складеність вимоги; другий аудитор розділу 5 (Дрєпіна) не знайшов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>BL-50</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>«при сумі від 2000 грн — 5 %, від 5000 грн — 10 %, від 10000 грн — 15 %» — діапазони перекриваються (сума 6000 грн одночасно «від 2000» і «від 5000»), межі не позначено як включні чи виключні.</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>«… обчислює знижку за обсяг: subtotal &lt; 2000 — 0 %; 2000 ≤ subtotal &lt; 5000 — 5 %; 5000 ≤ subtotal &lt; 10000 — 10 %; subtotal ≥ 10000 — 15 %; …»</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №18</t>
+        </is>
+      </c>
+      <c r="J33" s="22" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>BL-60</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Однозначність</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>п. 4 — вимога точна і допускає єдину інтерпретацію</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>«shippingFee(subtotalAfterDiscount) … якщо сума після знижки не менша за 1500 грн» — не визначено, яку знижку віднімають: лише за обсягом (BL-50) чи також за промокодом (BL-80).</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>«… де subtotalAfterDiscount = subtotal − знижка за обсяг (BL-50) − знижка за промокодом (BL-80); повертає 0.00 грн, якщо subtotalAfterDiscount не менша за 1500 грн, інакше 120.00 грн. …»</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №19</t>
+        </is>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>Пов'язано з рядком F-110 ↔ BL-60 (база порогу). Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>BL-70</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>Тестопридатність</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>практичний тест: тест-кейс з однозначним результатом «пройдено / не пройдено»</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>«Результат містить ознаку придатності та причину відмови» — можливі причини відмови не перелічено, тож тест не може перевірити, що повернуто правильну причину.</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>«… Причина відмови — одне зі значень: NOT_FOUND (код не існує), INVALID_FORMAT (довжина поза межами 6–10 символів), EXPIRED (дата закінчення раніша за today), ALREADY_USED (одноразовий код уже використано), INVALID_VALUE (значення поза допустимими межами); для придатного коду причина порожня.»</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №20</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>BL-80</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Здійсненність</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>виконання не залежить від систем, які продукт не контролює</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>«система перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх» — модуль не має доступу до даних сторонніх магазинів; до того ж за 2.3 бібліотека «без зовнішніх залежностей».</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>«Перед застосуванням одноразового коду метод перевіряє, що код не позначений як використаний у ШопЛайн; використаний код відхиляється (IllegalArgumentException із причиною відмови за BL-70).»</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>audit_drepina №11; audit_tymchak №21</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення збігаються (перевірка лише в межах ШопЛайн, IllegalArgumentException).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>BL-70, BL-80 (немає вимоги)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Повнота</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>п. 2 — усі необхідні вимоги присутні</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>BL-70: фіксована сума «не перевищує subtotal», BL-50: знижка за обсяг — до 15 % від subtotal; правила сумісного застосування знижок немає, тож сума до оплати може бути від'ємною (subtotal 2000, знижка за обсяг 100, промокод 2000 → −100).</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Нова вимога BL-90: «Сума до оплати = subtotal − знижка за обсяг (BL-50) − знижка за промокодом (BL-80); якщо результат менший за 0.00, він дорівнює 0.00; до суми до оплати додається вартість доставки (BL-60).»</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>новий</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>audit_tymchak №22</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J37"/>
+  <mergeCells count="1">
+    <mergeCell ref="L13:M20"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2:J37">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$H2="спірне"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_drepina" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_tymchak" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реєстр" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спірні" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Реєстр'!$A$1:$J$37</definedName>
@@ -5802,4 +5803,318 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Рядок реєстру</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Аргумент «за»</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Аргумент «проти»</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Рішення</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Хто вирішив / дата</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Пропозиція адвоката (чернетка до обговорення)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>№8 · F-50 · Тестопридатність
+Автор: Тимчак А. (ТА)
+Позначено ТА як спірне</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>F-50: «система показує текстове повідомлення про відсутність товарів» — текст не заданий. На demo виводиться «There are no products found.» (звірено 08.10.2026), але зі SRS цього не випливає: тест-кейс і розробник можуть очікувати різне формулювання (практичний тест чек-листа тестопридатності).</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Практичний тест тестопридатності проходить: результат «з'являється текстове повідомлення про відсутність товарів» перевіряється за наявністю повідомлення, число чи умова не відсутні. Точне формулювання — деталь дизайну. Виправлення лише називає текст і не додає ні числа, ні умови, ні способу спостереження, тобто за правилом «додає число — тестопридатність; уточнює об'єкт — однозначність» критерій обрано непослідовно: той самий випадок у №20 віднесено до однозначності.</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Відхилити як необґрунтований (немає порушеного пункту чек-листа), якщо автор не покаже, що без точного тексту результат «пройдено / не пройдено» неоднозначний. Якщо команда прийме — один критерій для №8 і №20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>№13 · F-110 ↔ розд. 2.3, п. 3 · Несуперечливість
+Автор: Тимчак А. (ТА)
+Позначено ТА як спірне</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Пряма суперечність: F-110 вимагає в підсумку замовлення «знижку за обсяг, знижку за промокодом і вартість доставки», а 2.3 каже, що модуль програми лояльності «в поточній версії ще не інтегрований в інтерфейс». Те саме зафіксовано в ризику 3 плану тестування. Порушено п. 2 чек-листа несуперечливості.</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Інші аудитори розділу 3 цього не позначили. Виправлення конфліктує з №12: воно прибирає знижки з підсумку, але лишає вартість доставки, правило якої (BL-60) теж належить неінтегрованому модулю, тож виправлення внутрішньо неповне. Вступ SRS: документ описує «поточну версію продукту та вимоги до нової функції», тож F-110 може описувати цільову поведінку нової функції, а не поточний UI. Тоді суперечності немає, є нечітка межа «поточне / нове».</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Прийняти як дефект, але не виправляти окремо від №12: ухвалити одне рішення для F-110. Варіант А — F-110 описує лише поточний UI (сума товарів), а знижки й доставка посилаються на розділ 5. Варіант Б — знижки й доставка в UI позначені як вимога нової функції. Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>№16 · GUI-10 · Повнота
+Автор: Коротка К. (КТ)
+Позначено ТА як спірне</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>GUI-10 називає «перемикач мови інтерфейсу», але не вказує, які мови доступні й яка мова за замовчуванням; тест не знає, що перевіряти (п. 1 чек-листа повноти). 2.2 фіксує лише, що інтерфейс demo англійською.</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Знайшов один автор із середньою впевненістю; другий аудитор розділу 4 не знайшов. Перелік DE, EL, EN, ES, FR, NL, TR узято з demo (звірено 08.10.2026), а не зі SRS. В ньому немає української, хоча замовник — українська компанія (Житомир), а план тестування (тип 14) спирається на українські формати. Виправлення фіксує набір мов, який може не відповідати потребам замовника: це рішення замовника, а не дефект тексту.</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Прийняти лише як питання замовнику: «які мови підтримує перемикач, чи є українська і яка мова за замовчуванням». Конкретний набір мов у SRS 1.1 не вносити без підтвердження замовником. Інакше відхилити.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>№20 · GUI-70 · Однозначність
+Автор: Коротка К. (КТ)
+Позначено ТА як спірне</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>GUI-70: «Порожній кошик відображає текстове повідомлення замість таблиці» — текст не заданий; тест-кейс не має точного очікуваного результату. Авторка пропонує «The cart is empty».</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Те саме, що №8: перевірка наявності повідомлення замість таблиці однозначна, формулювання тексту — дизайн. Авторка сама вказала середню впевненість, другий аудитор розділу 4 не знайшов. Запропонований текст на demo не звірено. Критерій (однозначність) відрізняється від №8 (тестопридатність) для того самого типу дефекту.</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Розглядати разом із №8 і ухвалити однакове рішення: відхилити, або прийняти обидва під одним критерієм. Текст повідомлення — потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>№31 · BL-40 · Простежуваність
+Автор: Тимчак А. (ТА)
+Позначено ТА як спірне</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>BL-40 під одним ID описує чотири методи (removeItem, changeQty, subtotal, itemCount). Юніт-тест (спринт 4) і матриця простежуваності (спринт 5) не можуть послатися на окрему вимогу.</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Названий п. 4 чек-листа простежуваності перевіряє, чи формат ID дозволяє розділяти вимогу без впливу на решту ID; формат із кроком 10 це дозволяє, тож порушення цього пункту немає. Складеність вимоги — це питання атомарності, якого в шести чек-листах немає; пункти 1 і 5 стосуються дублів і перекриття. Другий аудитор розділу 5 не знайшов. Виправлення створює три нові ID (BL-42, BL-44, BL-46) і змінює структуру розділу, не усуваючи порушення названого пункту.</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Відхилити: названий пункт чек-листа не порушено. Якщо команда хоче залишити рядок, потрібен інший порушений пункт; без нього рядок не рахувати до нормативу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>№12 F-110 ↔ BL-60 (несуперечливість) + №33 BL-60 (однозначність)
+Автори: усі четверо / Тимчак А. (ТА)
+Додано адвокатом: різні виправлення одного питання</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Суперечність порогу безкоштовної доставки підтверджують усі четверо аудиторів (№12), а BL-60 не уточнює, яка саме знижка віднімається (№33). Обидва дефекти справжні, виправлення потрібні.</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Автори пропонують різну базу порогу: після знижки за обсяг (Горбонос, Дрєпіна) або після всіх знижок (Тимчак, Коротка). Беклог спринта 1 підтримує другий варіант: US-08 «поріг рахується від суми після знижок, а не до них», US-09 «сума кошика після знижок перевищує поріг». Поріг 1500 і 2000 грн — теж припущення. US-09 каже «перевищує», BL-60 — «не менша за»: межа «сума дорівнює порогу» не узгоджена. Прийняті як є, обидва рядки дадуть SRS 1.1 дві різні бази порогу.</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Об'єднати №12 і №33 в одне рішення: база порогу = сума після знижки за обсяг і знижки за промокодом (за US-08/US-09), поріг 1500 грн за BL-60, межа «не менша за». Однаково відобразити в F-110 і BL-60. Поріг і межа — потребують підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>№32 · BL-50 · Однозначність
+Автор: Тимчак А. (ТА)
+Додано адвокатом</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>BL-50: «при сумі від 2000 грн — 5 %, від 5000 грн — 10 %, від 10000 грн — 15 %». Діапазони формально перекриваються (6000 грн одночасно «від 2000» і «від 5000»), межі не названо включними чи виключними.</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>«Від N» означає нижню межу включно, а застосування лише найвищого рівня випливає з беклогу: US-06 «межі трьох рівнів суми (тест на ±1 грн від порогу), застосування лише найвищого рівня». Отже, є єдина інтерпретація і п. 4 чек-листа однозначності не порушено. Виправлення лише переписує ті самі правила нерівностями.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Відхилити як необґрунтований, або перевести в рекомендацію (запис нерівностями) без підрахунку до нормативу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>№34 · BL-70 · Тестопридатність
+Автор: Тимчак А. (ТА)
+Додано адвокатом</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>BL-70: «Результат містить ознаку придатності та причину відмови» — перелік причин не заданий; тест не може перевірити, яку саме причину повернуто.</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Причини однозначно виводяться з п'яти умов самого BL-70 (довжина, дата, одноразовість, відсоток, фіксована сума). Виправлення додає значення NOT_FOUND («код не існує»), якого в SRS немає: validate(code, today, subtotal) не має реєстру кодів, тож це нова поведінка без основи, тобто виправлення породжує новий дефект. Воно також змінює тип «причини» (текст → перелік кодів) без позначки «потребує підтвердження замовником».</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Прийняти дефект, але переписати виправлення: прибрати NOT_FOUND, зв'язати по одній причині з кожною умовою BL-70, позначити «потребує підтвердження замовником».</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>№36 · BL-70, BL-80 (немає вимоги) · Повнота
+Автор: Тимчак А. (ТА)
+Додано адвокатом</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Реальна прогалина (п. 2 чек-листа повноти): BL-70 дозволяє фіксований промокод до subtotal, а BL-50 дає знижку за обсяг окремо. Для subtotal 2000 грн: 2000 − 100 (5 %) − 2000 (промокод) = −100 грн. Правил сумісного застосування знижок немає.</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Виправлення додає нову вимогу BL-90, яка вирішує бізнес-питання (обрізання до 0.00) без позначки «потребує підтвердження замовником»: колонка «Примітка» порожня. Воно додає до суми вартість доставки, чого немає в BL-60 (shippingFee лише повертає вартість) — це вихід за межі дефекту. Методу «сума до оплати» в модулі немає, тож BL-90 вимагає нового API. Знайшов один автор. Простіше виправлення: обмежити фіксований промокод у BL-70 значенням subtotal мінус знижка за обсяг.</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Прийняти дефект, але переписати виправлення: або обмеження в BL-70 (фіксована сума не більша за subtotal мінус знижка за обсяг), або BL-90 лише з обрізанням до 0.00 і без доставки. Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>ШопЛайн · Спринт 2 · 08.10.2026 · Аркуш веде: Горбонос О. (СМ), «адвокат замовника».</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Рядки №8, 13, 16, 20, 31 позначила ТА як «спірне»; решту додано адвокатом за результатами перевірки реєстру (36 рядків) проти SRS 1.0 і беклогу спринта 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Стовпці «Рішення» і «Хто вирішив / дата» заповнюються після обговорення командою за модерації КТ; стовпець «Пропозиція адвоката» — чернетка, не рішення. Необґрунтовані рядки позначаються «відхилено після обговорення» і лишаються в «Реєстрі» зі статусом.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -5999,14 +5999,14 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Автори пропонують різну базу порогу: після знижки за обсяг (Горбонос, Дрєпіна) або після всіх знижок (Тимчак, Коротка). Беклог спринта 1 підтримує другий варіант: US-08 «поріг рахується від суми після знижок, а не до них», US-09 «сума кошика після знижок перевищує поріг». Поріг 1500 і 2000 грн — теж припущення. US-09 каже «перевищує», BL-60 — «не менша за»: межа «сума дорівнює порогу» не узгоджена. Прийняті як є, обидва рядки дадуть SRS 1.1 дві різні бази порогу.</t>
+          <t>Автори пропонують різну базу порогу: після знижки за обсяг (Горбонос, Дрєпіна) або після всіх знижок (Тимчак, Коротка). Беклог спринта 1 схиляє до другого варіанту (але не доводить його): US-08 «поріг рахується від суми після знижок, а не до них», US-09 «сума кошика після знижок перевищує поріг». Поріг 1500 і 2000 грн — теж припущення. US-09 каже «перевищує» (строго більше), BL-60 — «не менша за» (більше або дорівнює); у US-09 випадок «сума точно дорівнює порогу» названо лише тестовим, тож межа не узгоджена. З іншого боку, BL-60 називає параметр subtotalAfterDiscount у класі DiscountCalculator, який рахує лише знижку за обсяг (промокод — окремий клас PromoCodeValidator), тож буквальне читання BL-60 — після знижки за обсяг: саме ця неоднозначність і є дефектом №33. Прийняті як є, обидва рядки дадуть SRS 1.1 дві різні бази порогу.</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Об'єднати №12 і №33 в одне рішення: база порогу = сума після знижки за обсяг і знижки за промокодом (за US-08/US-09), поріг 1500 грн за BL-60, межа «не менша за». Однаково відобразити в F-110 і BL-60. Поріг і межа — потребують підтвердження замовником.</t>
+          <t>Об'єднати №12 і №33 в одне рішення: база порогу = сума після знижки за обсяг і знижки за промокодом (так схиляє беклог US-08/US-09), поріг 1500 грн за BL-60, межа «не менша за». Однаково відобразити в F-110 і BL-60. База, поріг і межа — потребують підтвердження замовником.</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -3950,7 +3950,7 @@
       </c>
       <c r="H2" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I2" s="22" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="H3" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I3" s="22" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H4" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>спірне</t>
+          <t>відхилено після обговорення</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="H11" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>спірне</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>спірне</t>
+          <t>відхилено після обговорення</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>спірне</t>
+          <t>відхилено після обговорення</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="H24" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="H26" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="H28" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="H29" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H30" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="H32" s="22" t="inlineStr">
         <is>
-          <t>спірне</t>
+          <t>відхилено після обговорення</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="H33" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>відхилено після обговорення</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="H34" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="H35" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="H36" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I36" s="22" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="H37" s="22" t="inlineStr">
         <is>
-          <t>новий</t>
+          <t>прийнято</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -5872,8 +5872,16 @@
           <t>Практичний тест тестопридатності проходить: результат «з'являється текстове повідомлення про відсутність товарів» перевіряється за наявністю повідомлення, число чи умова не відсутні. Точне формулювання — деталь дизайну. Виправлення лише називає текст і не додає ні числа, ні умови, ні способу спостереження, тобто за правилом «додає число — тестопридатність; уточнює об'єкт — однозначність» критерій обрано непослідовно: той самий випадок у №20 віднесено до однозначності.</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Відхилено після обговорення: наявність повідомлення про відсутність товарів перевіряється однозначно, порушеного пункту чек-листа немає; точний текст — деталь дизайну. Рішення однакове з №20.</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Відхилити як необґрунтований (немає порушеного пункту чек-листа), якщо автор не покаже, що без точного тексту результат «пройдено / не пройдено» неоднозначний. Якщо команда прийме — один критерій для №8 і №20.</t>
@@ -5898,8 +5906,16 @@
           <t>Інші аудитори розділу 3 цього не позначили. Виправлення конфліктує з №12: воно прибирає знижки з підсумку, але лишає вартість доставки, правило якої (BL-60) теж належить неінтегрованому модулю, тож виправлення внутрішньо неповне. Вступ SRS: документ описує «поточну версію продукту та вимоги до нової функції», тож F-110 може описувати цільову поведінку нової функції, а не поточний UI. Тоді суперечності немає, є нечітка межа «поточне / нове».</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Прийнято (несуперечливість, п. 2). Окремо не виправляється: F-110 правиться одним рішенням разом із №12 і №33 — знижки й доставка в підсумку замовлення позначаються як вимога нової функції. Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Прийняти як дефект, але не виправляти окремо від №12: ухвалити одне рішення для F-110. Варіант А — F-110 описує лише поточний UI (сума товарів), а знижки й доставка посилаються на розділ 5. Варіант Б — знижки й доставка в UI позначені як вимога нової функції. Потребує підтвердження замовником.</t>
@@ -5924,8 +5940,16 @@
           <t>Знайшов один автор із середньою впевненістю; другий аудитор розділу 4 не знайшов. Перелік DE, EL, EN, ES, FR, NL, TR узято з demo (звірено 08.10.2026), а не зі SRS. В ньому немає української, хоча замовник — українська компанія (Житомир), а план тестування (тип 14) спирається на українські формати. Виправлення фіксує набір мов, який може не відповідати потребам замовника: це рішення замовника, а не дефект тексту.</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Відхилено після обговорення як дефект SRS: перелік мов узято з demo, а не зі SRS, і він може не відповідати потребам замовника. Винесено питанням замовнику на демо: які мови підтримує перемикач, чи є українська, яка мова за замовчуванням.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Прийняти лише як питання замовнику: «які мови підтримує перемикач, чи є українська і яка мова за замовчуванням». Конкретний набір мов у SRS 1.1 не вносити без підтвердження замовником. Інакше відхилити.</t>
@@ -5950,8 +5974,16 @@
           <t>Те саме, що №8: перевірка наявності повідомлення замість таблиці однозначна, формулювання тексту — дизайн. Авторка сама вказала середню впевненість, другий аудитор розділу 4 не знайшов. Запропонований текст на demo не звірено. Критерій (однозначність) відрізняється від №8 (тестопридатність) для того самого типу дефекту.</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Відхилено після обговорення: як і №8, наявність повідомлення замість таблиці перевіряється однозначно; точний текст — деталь дизайну.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Розглядати разом із №8 і ухвалити однакове рішення: відхилити, або прийняти обидва під одним критерієм. Текст повідомлення — потребує підтвердження замовником.</t>
@@ -5976,8 +6008,16 @@
           <t>Названий п. 4 чек-листа простежуваності перевіряє, чи формат ID дозволяє розділяти вимогу без впливу на решту ID; формат із кроком 10 це дозволяє, тож порушення цього пункту немає. Складеність вимоги — це питання атомарності, якого в шести чек-листах немає; пункти 1 і 5 стосуються дублів і перекриття. Другий аудитор розділу 5 не знайшов. Виправлення створює три нові ID (BL-42, BL-44, BL-46) і змінює структуру розділу, не усуваючи порушення названого пункту.</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Відхилено після обговорення: п. 4 чек-листа простежуваності не порушено — формат ID із кроком 10 дозволяє розділити вимогу без впливу на решту ID; інших порушених пунктів не названо.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Відхилити: названий пункт чек-листа не порушено. Якщо команда хоче залишити рядок, потрібен інший порушений пункт; без нього рядок не рахувати до нормативу.</t>
@@ -6002,8 +6042,16 @@
           <t>Автори пропонують різну базу порогу: після знижки за обсяг (Горбонос, Дрєпіна) або після всіх знижок (Тимчак, Коротка). Беклог спринта 1 схиляє до другого варіанту (але не доводить його): US-08 «поріг рахується від суми після знижок, а не до них», US-09 «сума кошика після знижок перевищує поріг». Поріг 1500 і 2000 грн — теж припущення. US-09 каже «перевищує» (строго більше), BL-60 — «не менша за» (більше або дорівнює); у US-09 випадок «сума точно дорівнює порогу» названо лише тестовим, тож межа не узгоджена. З іншого боку, BL-60 називає параметр subtotalAfterDiscount у класі DiscountCalculator, який рахує лише знижку за обсяг (промокод — окремий клас PromoCodeValidator), тож буквальне читання BL-60 — після знижки за обсяг: саме ця неоднозначність і є дефектом №33. Прийняті як є, обидва рядки дадуть SRS 1.1 дві різні бази порогу.</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Прийнято обидва (№12 — несуперечливість, №33 — однозначність). Одне рішення для F-110 і BL-60: база порогу — сума після знижки за обсяг і знижки за промокодом, поріг 1500 грн, межа «не менша за». Потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Об'єднати №12 і №33 в одне рішення: база порогу = сума після знижки за обсяг і знижки за промокодом (так схиляє беклог US-08/US-09), поріг 1500 грн за BL-60, межа «не менша за». Однаково відобразити в F-110 і BL-60. База, поріг і межа — потребують підтвердження замовником.</t>
@@ -6028,8 +6076,16 @@
           <t>«Від N» означає нижню межу включно, а застосування лише найвищого рівня випливає з беклогу: US-06 «межі трьох рівнів суми (тест на ±1 грн від порогу), застосування лише найвищого рівня». Отже, є єдина інтерпретація і п. 4 чек-листа однозначності не порушено. Виправлення лише переписує ті самі правила нерівностями.</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Відхилено після обговорення: «від N» — нижня межа включно, застосовується лише найвищий рівень (US-06); єдина інтерпретація існує, п. 4 не порушено.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Відхилити як необґрунтований, або перевести в рекомендацію (запис нерівностями) без підрахунку до нормативу.</t>
@@ -6054,8 +6110,16 @@
           <t>Причини однозначно виводяться з п'яти умов самого BL-70 (довжина, дата, одноразовість, відсоток, фіксована сума). Виправлення додає значення NOT_FOUND («код не існує»), якого в SRS немає: validate(code, today, subtotal) не має реєстру кодів, тож це нова поведінка без основи, тобто виправлення породжує новий дефект. Воно також змінює тип «причини» (текст → перелік кодів) без позначки «потребує підтвердження замовником».</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Прийнято (тестопридатність). Виправлення переписує ТА перед SRS 1.1: прибрати NOT_FOUND, по одній причині на кожну умову BL-70, позначка «потребує підтвердження замовником».</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Прийняти дефект, але переписати виправлення: прибрати NOT_FOUND, зв'язати по одній причині з кожною умовою BL-70, позначити «потребує підтвердження замовником».</t>
@@ -6080,8 +6144,16 @@
           <t>Виправлення додає нову вимогу BL-90, яка вирішує бізнес-питання (обрізання до 0.00) без позначки «потребує підтвердження замовником»: колонка «Примітка» порожня. Воно додає до суми вартість доставки, чого немає в BL-60 (shippingFee лише повертає вартість) — це вихід за межі дефекту. Методу «сума до оплати» в модулі немає, тож BL-90 вимагає нового API. Знайшов один автор. Простіше виправлення: обмежити фіксований промокод у BL-70 значенням subtotal мінус знижка за обсяг.</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Прийнято (повнота, п. 2). Виправлення переписує ТА перед SRS 1.1: обмежити фіксований промокод у BL-70 (не більше subtotal мінус знижка за обсяг) або BL-90 лише з обрізанням до 0.00 і без доставки; потребує підтвердження замовником.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Команда (модерація: Коротка К., КТ), 08.10.2026</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Прийняти дефект, але переписати виправлення: або обмеження в BL-70 (фіксована сума не більша за subtotal мінус знижка за обсяг), або BL-90 лише з обрізанням до 0.00 і без доставки. Потребує підтвердження замовником.</t>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -3909,7 +3909,7 @@
       </c>
       <c r="M1" s="11" t="inlineStr">
         <is>
-          <t>Рядків</t>
+          <t>Прийнято</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="M2" s="23">
-        <f>COUNTIF($C$2:$C$37,L2)</f>
+        <f>COUNTIFS($C$2:$C$37,L2,$H$2:$H$37,"прийнято")</f>
         <v/>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="M3" s="23">
-        <f>COUNTIF($C$2:$C$37,L3)</f>
+        <f>COUNTIFS($C$2:$C$37,L3,$H$2:$H$37,"прийнято")</f>
         <v/>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="M4" s="23">
-        <f>COUNTIF($C$2:$C$37,L4)</f>
+        <f>COUNTIFS($C$2:$C$37,L4,$H$2:$H$37,"прийнято")</f>
         <v/>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="M5" s="23">
-        <f>COUNTIF($C$2:$C$37,L5)</f>
+        <f>COUNTIFS($C$2:$C$37,L5,$H$2:$H$37,"прийнято")</f>
         <v/>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="M6" s="23">
-        <f>COUNTIF($C$2:$C$37,L6)</f>
+        <f>COUNTIFS($C$2:$C$37,L6,$H$2:$H$37,"прийнято")</f>
         <v/>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="M7" s="23">
-        <f>COUNTIF($C$2:$C$37,L7)</f>
+        <f>COUNTIFS($C$2:$C$37,L7,$H$2:$H$37,"прийнято")</f>
         <v/>
       </c>
     </row>
@@ -4432,11 +4432,11 @@
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t>Статус «спірне»</t>
+          <t>Відхилено після обговорення</t>
         </is>
       </c>
       <c r="M10" s="23">
-        <f>COUNTIF($H$2:$H$37,"спірне")</f>
+        <f>COUNTIF($H$2:$H$37,"відхилено після обговорення")</f>
         <v/>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -5675,7 +5675,7 @@
       </c>
       <c r="F35" s="22" t="inlineStr">
         <is>
-          <t>«… Причина відмови — одне зі значень: NOT_FOUND (код не існує), INVALID_FORMAT (довжина поза межами 6–10 символів), EXPIRED (дата закінчення раніша за today), ALREADY_USED (одноразовий код уже використано), INVALID_VALUE (значення поза допустимими межами); для придатного коду причина порожня.»</t>
+          <t>«… Результат містить ознаку придатності та причину відмови — по одній на кожну умову: INVALID_LENGTH (довжина коду поза межами 6–10 символів), EXPIRED (дата закінчення дії раніша за today), ALREADY_USED (одноразовий код уже використано), INVALID_PERCENT (для типу «відсоток» значення поза межами 1–50 включно), INVALID_AMOUNT (для типу «фіксована сума» значення не більше 0 або перевищує допустиму межу за BL-70); якщо не виконано кілька умов, повертається причина першої з них у цьому порядку; для придатного коду причина порожня.»</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -5693,7 +5693,11 @@
           <t>audit_tymchak №20</t>
         </is>
       </c>
-      <c r="J35" s="22" t="n"/>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>Переписано за рішенням команди (SCRUM-55, аркуш «Спірні»): прибрано NOT_FOUND (у SRS немає реєстру кодів), по одній причині на кожну з п'яти умов BL-70. Назви причин і порядок перевірки — потребує підтвердження замовником.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="n">
@@ -5771,7 +5775,7 @@
       </c>
       <c r="F37" s="22" t="inlineStr">
         <is>
-          <t>Нова вимога BL-90: «Сума до оплати = subtotal − знижка за обсяг (BL-50) − знижка за промокодом (BL-80); якщо результат менший за 0.00, він дорівнює 0.00; до суми до оплати додається вартість доставки (BL-60).»</t>
+          <t>Обмежити фіксований промокод у BL-70: «… для типу «фіксована сума» значення більше 0 і не перевищує subtotal мінус знижка за обсяг (BL-50) …». Тоді сума до оплати не може бути від'ємною: відсотковий промокод — не більше 50 %, знижка за обсяг — не більше 15 %. Нова вимога BL-90 не потрібна.</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -5789,7 +5793,11 @@
           <t>audit_tymchak №22</t>
         </is>
       </c>
-      <c r="J37" s="22" t="n"/>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>Переписано за рішенням команди (SCRUM-55, аркуш «Спірні»): обрано варіант з обмеженням у BL-70 замість BL-90; вартість доставки не зачіпається. Пов'язано з рядком №34 (причина INVALID_AMOUNT). Потребує підтвердження замовником.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J37"/>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -4572,8 +4572,7 @@
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>Варіант Горбонос О. (СМ), Дрєпіна А. (ІТ): У F-110: «… вартість доставки: 120 грн; якщо сума замовлення після знижки за обсяг становить не менше 1500 грн, доставка безкоштовна.» (Поріг 1500 грн узято з BL-60 — потребує підтвердження замовником.)
-Варіант Тимчак А. (ТА), Коротка К. (КТ): F-110: «… вартість доставки визначається за BL-60: 0.00 грн, якщо сума після знижок не менша за 1500 грн, інакше 120.00 грн.»</t>
+          <t>F-110: «… вартість доставки визначається за BL-60: 0.00 грн, якщо сума після знижки за обсяг (BL-50) і знижки за промокодом (BL-80) не менша за 1500 грн, інакше 120.00 грн.» Формулювання збігається з виправленням BL-60 (рядок №33). База порогу, поріг і межа — потребують підтвердження замовником.</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -4593,7 +4592,7 @@
       </c>
       <c r="J13" s="22" t="inlineStr">
         <is>
-          <t>Варіанти різняться базою порогу: сума після знижки за обсяг (Горбонос, Дрєпіна) чи після всіх знижок (Тимчак, Коротка) — пов'язано з рядком BL-60 (однозначність). Поріг — потребує підтвердження замовником.</t>
+          <t>Переписано за рішенням команди (SCRUM-55, аркуш «Спірні»): одне рішення для F-110 і BL-60 разом із №33 — база порогу = сума після знижки за обсяг і знижки за промокодом, поріг 1500 грн, межа «не менша за»; попередні варіанти авторів зведено в один. Знижки й доставка в підсумку замовлення — вимога нової функції (№13). Потребує підтвердження замовником.</t>
         </is>
       </c>
       <c r="L13" s="24" t="inlineStr">
@@ -4628,7 +4627,7 @@
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>F-110: «Підсумок замовлення містить суму товарів і вартість доставки; знижка за обсяг і знижка за промокодом у версії 1.0 в інтерфейсі не відображаються (розд. 2.3).»</t>
+          <t>Окремо не виправляється: F-110 правиться одним рішенням разом із №12 і №33. У F-110 знижки й вартість доставки в підсумку замовлення позначаються як вимога нової функції: «Підсумок замовлення містить суму товарів; як вимога нової функції (модуль програми лояльності, розд. 2.3) — також знижку за обсяг, знижку за промокодом і вартість доставки за BL-60.» Потребує підтвердження замовником.</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -4648,7 +4647,7 @@
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>Сумнівний: інші аудитори розділу 3 цього не позначили; виправлення конфліктує з варіантами виправлення рядка F-110 ↔ BL-60, які залишають знижки в підсумку. Альтернатива — інтегрувати модуль і змінити 2.3.</t>
+          <t>Прийнято за рішенням команди (SCRUM-55, аркуш «Спірні»): суперечність F-110 і розд. 2.3 усувається позначкою «вимога нової функції», а не вилученням знижок із підсумку; виправлення спільне з №12 і №33. Потребує підтвердження замовником.</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_tymchak" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реєстр" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спірні" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рецензування" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Реєстр'!$A$1:$J$37</definedName>
@@ -138,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,6 +201,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6189,4 +6193,2607 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Артефакт/рядок</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Автор</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Рецензент</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>Перевірені пункти</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>Зауваження</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>Виправлено (дата)</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>Повторне підтвердження (ПІБ, дата)</t>
+        </is>
+      </c>
+      <c r="J1" s="25" t="inlineStr">
+        <is>
+          <t>Результат</t>
+        </is>
+      </c>
+      <c r="K1" s="25" t="inlineStr">
+        <is>
+          <t>Рядків</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №1 · 2.2 ↔ розд. 6 (вимога про 375 px, без ID) · Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент.</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="J2" s="26" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="K2" s="26">
+        <f>COUNTIF($E$2:$E$72,J2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №2 · F-10 · Повнота</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>Виправлення робить «область (штат)» необов'язковою, але на demo поле state обов'язкове (aria-required=true у формі реєстрації, перевірено 12.10.2026), а F-110 (крок 3) включає область до адреси доставки. Узгодити: або «область» стає обов'язковою, або змінити F-110; позначити «потребує підтвердження замовником». Повернено ТА.</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="J3" s="26" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="K3" s="26">
+        <f>COUNTIF($E$2:$E$72,J3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №3 · F-10 · Повнота</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: текст «A customer with this email address already exists.» не звірено з demo (потрібна реєстрація з наявним email); у Примітці вже стоїть «потребує підтвердження замовником».</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="n"/>
+      <c r="H4" s="22" t="n"/>
+      <c r="J4" s="26" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="K4" s="26">
+        <f>COUNTIF($E$2:$E$72,J4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №4 · F-20 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>очікує SRS 1.1</t>
+        </is>
+      </c>
+      <c r="K5" s="26">
+        <f>COUNTIF($E$2:$E$72,J5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №5 · F-30 · Здійсненність</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="J6" s="27" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="K6" s="26">
+        <f>SUM(K2:K5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №6 · F-40 ↔ GUI-20 · Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент (усі четверо автори; рядок розглянуто через «Спірні», рішення команди).</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №7 · F-50 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Звірено на demo через API: дві категорії 7+3=10 товарів (об'єднання, «АБО»); два бренди 40+10=50; категорія+бренд = 6 ≤ 7 (перетин, «І»). Виправлення відповідає поведінці demo.</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №8 · F-50 · Тестопридатність</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4–6 н/з 7✓</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Рядок відхилено: рішення «відхилено після обговорення» і підпис КТ (08.10.2026) є в «Спірні». Редакційне (ТА): Примітка в «Реєстрі» містить чернетку («узгодити один критерій») — замінити посиланням на рішення «Спірні».</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №9 · F-60 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №10 · F-90 · Тестопридатність</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №11 · F-100 · Повнота</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент.</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №12 · F-110 ↔ BL-60 · Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент (усі четверо автори; рядок розглянуто через «Спірні», рішення команди). Рядок переписано в PR #23 (SCRUM-56).</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №13 · F-110 ↔ розд. 2.3, пункт 3 · Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>На main виправлення (вилучити знижки з підсумку) суперечить рішенню SCRUM-55 («вимога нової функції») і виправленню №12. Переписано в PR #23 (SCRUM-56, відкритий, approve КТ 10.10). Повторне підтвердження — після merge.</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №14 · F-120 ↔ GUI-40 · Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент (усі четверо автори; рядок розглянуто через «Спірні», рішення команди). Рядок переписано в PR #23 (SCRUM-56).</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №15 · F-140 · Повнота</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>очікує КТ</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №16 · GUI-10 · Повнота</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4–6 н/з 7✓</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>Рядок відхилено; рішення (питання замовнику на демо про мови перемикача) зафіксовано в «Спірні». Редакційне (ТА): Примітка «Сумнівний…» застаріла — додати посилання на рішення.</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №17 · GUI-30 ↔ BL-10, BL-40 · Несуперечливість</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Цитати дослівні: GUI-30 «від 0 до 100»; BL-10 і BL-40 «від 1 до 99 включно». Три виправлення збігаються.</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №18 · GUI-50 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>Пп. 1 і 4 однозначності названо за офіційним чек-листом; «або» дає два допустимі місця виведення — дефект підтверджено.</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №19 · GUI-60 (два рядки) · Простежуваність</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Дублікат підтверджено в SRS 1.0 (два рядки GUI-60 у розд. 4). GUI-65 вільний (крок 10), решта ID не змінюється.</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №20 · GUI-70 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4–6 н/з 7✓</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>Рядок відхилено; рішення зафіксовано в «Спірні». Редакційне (ТА): Примітка («Сумнівний…») застаріла.</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №21 · GUI-80 · Здійсненність</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>Розрахунок автора перевірено: 7680×4320×3 байти ≈ 99,5 МБ; за 50 мс це ≈ 16 Гбіт/с. Два виправлення суперечать одне одному (≥1200×1200 / ≤800×800) — ТА обирає один варіант до внесення в SRS 1.1 (перевіряється в рядках «SRS 1.1» нижче).</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №22 · GUI-100 · Тестопридатність</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>GUI-100 існує в SRS (ID розбито переносом «GUI-/100»); показники вимірювані (4,5:1; 3:1; 14 px), позначка замовника є.</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №23 · P-10 · Здійсненність</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>P-20 дозволяє відповідь API до 1 с, тому 0,1 с для сторінки нереальні — здійсненність підтверджено. Варіанти різні (3 с / 10 Мбіт/с; 2 с / 15 Мбіт/с) — обрати один до SRS 1.1.</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №24 · S-10 · Тестопридатність</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти КТ і ІТ сумісні (bcrypt, HTTPS) — об'єднати до SRS 1.1. Головний критерій — тестопридатність (пояснено в Примітці), «не містить вразливостей» порушує ще й здійсненність.</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №25 · U-10 · Тестопридатність</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>Варіанти різняться методикою (4 з 5 / 90 % з 10); план (тип 3) використовує варіант ІТ — після вибору варіанта синхронізувати.</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №26 · розд. 6, між U-20 і D-10 (без ID) · Простежуваність</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>Локатор існує: окремий рядок розд. 6 між U-20 і D-10 без ID. U-30 вільний (U-10, U-20 → крок 10).</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №27 · D-10 · Повнота</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>«Регламент … ШопЛайн-ЛП-2025» у 1.4 «Посилання» відсутній (4 пункти) — підтверджено.</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №28 · BL-10 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: «unitPrice &gt; 0» в описі — скорочення автора в лапках, не цитата SRS (решта цитат дослівні). Виправлення №28 і №29 правлять одне речення BL-10 — у SRS 1.1 вносити одним записом, щоб не втратити «name».</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №29 · BL-10 · Повнота</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: правило «name — непорожній рядок» є новою вимогою — додати в Примітку «потребує підтвердження замовником».</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №30 · BL-30 ↔ BL-20 · Простежуваність</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>BL-30 за змістом повторює BL-20 (BL-20 повніше: ліміт 99); вилучення BL-30 без перевикористання номера відповідає п. 1 простежуваності.</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №31 · BL-40 · Простежуваність</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4–6 н/з 7✓</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>Рядок відхилено; рішення зафіксовано в «Спірні». Редакційне (ТА): Примітка застаріла — додати посилання на рішення.</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №32 · BL-50 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4–6 н/з 7✓</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>Рядок відхилено; рішення (US-06) зафіксовано в «Спірні». Редакційне (ТА): Примітка порожня — додати посилання на рішення.</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №33 · BL-60 · Однозначність</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>База порогу збігається з рішенням SCRUM-55 і виправленням №12 (PR #23): subtotal − знижка за обсяг − знижка за промокодом, межа «не менша за».</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №34 · BL-70 · Тестопридатність</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>На main виправлення вводить NOT_FOUND (у SRS немає реєстру кодів) і INVALID_VALUE без позначки замовника — нова поведінка (рішення SCRUM-55). Переписано в PR #23. Зауваження СМ до PR: у INVALID_AMOUNT замінити «допустиму межу за BL-70» на «subtotal мінус знижка за обсяг (BL-50)».</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №35 · BL-80 · Здійсненність</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: виправлення звужує правило замовника (перевірка лише в межах ШопЛайн) — додати «потребує підтвердження замовником».</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Реєстр №36 · BL-70, BL-80 (немає вимоги) · Повнота</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>На main BL-90 додає вартість доставки (поза BL-60) і бізнес-правило обрізання без позначки замовника (рішення SCRUM-55). Переписано в PR #23 (обмеження в BL-70). Зауваження СМ до PR: у Примітці вказати, що варіант обрала ТА з двох, дозволених рішенням команди.</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>План · рівень 1. Модульне (Unit)</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>Межі qty 0/1/99/100 відповідають BL-10/BL-40; пороги BL-50 (1999.99 … 10000.00) — зі SRS.</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>План · рівень 2. Інтеграційне</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: джерело кодів 200/422 не випливає зі SRS — вказати (валідація Laravel на demo) або прибрати.</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>План · рівень 3. Димове (Smoke)</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>1✗ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>Ціль загальна («основні критичні функції») — не називає об'єкт і ризик ШопЛайн (напр., недоступний чекаут блокує всі подальші перевірки). Опис і дані конкретні.</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>План · рівень 4. Системне</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>1✗ 2✓ 3✗ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>Ціль загальна; у «Інструменти / Дані» немає даних (обліковий запис, товари, промокод) — додати.</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>План · рівень 5. Альфа-тестування</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>На demo не виконується — позначено. Редакційне: пріоритет Medium не названо в 2.1 — додати.</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>План · рівень 6. Бета-тестування</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>1✗ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>Ціль загальна (годиться для будь-якого продукту) — назвати об'єкт і ризик ШопЛайн. Опис конкретний, обмеження demo позначено.</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>План · рівень 7. Приймальне замовником (UAT)</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>Ціль називає замовника; на demo не виконується — позначено.</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 1 · Функціональне</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>Combination Pliers є на demo (перевірено через API 12.10.2026); критерій успіху названо.</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 2 · Графічного інтерфейсу (GUI)</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>Значення «9 карток» і «1–99» узято з виправлень №6 і №17 (у SRS 1.0: 12 карток, 0–100); SRS 1.1 ще немає — перевірити після випуску.</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n"/>
+      <c r="H46" s="22" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 3 · Юзабіліті</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✗ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>Невиконуваний/суперечливий опис: пошук «Hammer» «через фільтр брендів» (Hammer — товар, не бренд); вибірка 10 учасників «на етапі UAT/альфа», а в Інструментах — «на Toolshop»; не вказано, де виконується. Вибірка 10 залежить від вибору варіанта U-10 у №25 (КТ: 5 учасників).</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="22" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 4 · Захищеності</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>Редирект /account → /auth/login для гостя підтверджено на demo (12.10.2026); обмеження demo і позначки замовника є. Редакційне: S-20 вимагає також недоступності кроків 3–4 для гостя — додати крок.</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="n"/>
+      <c r="H48" s="22" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 5 · Потоків даних</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: у критерії «≥ 1500 грн» немає позначки — рішення SCRUM-55 вимагає її для бази, порогу й межі.</t>
+        </is>
+      </c>
+      <c r="G49" s="22" t="n"/>
+      <c r="H49" s="22" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 6 · Інтерфейсів (програмних)</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>Перевірено на API demo: GET /products (поля id, name, price, in_stock), GET /categories — відповідають опису; POST /users/login не надсилала (потрібні облікові дані). Обмеження щодо HTTP 500 позначено.</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="22" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 7 · Інсталяційне</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>Незастосовність пояснено природою продукту (вебзастосунок, дистрибутива немає).</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="n"/>
+      <c r="H51" s="22" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 8 · Конфігураційне</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: «U-30» — запропонований ID (реєстр №26), у SRS 1.0 його немає; залежить від рішення №1 (2.2 ↔ розд. 6) — позначити.</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="n"/>
+      <c r="H52" s="22" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 9 · Об'ємне</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>Обмеження demo (52 товари, 6 сторінок, по 9) позначено й відповідає перевірці на demo.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="n"/>
+      <c r="H53" s="22" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 10 · Надійності</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>Сценарій 30 хв, 6 сторінок, ≥ 5 операцій, критерій успіху названо.</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 11 · Доступності (Availability)</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>Незастосовність пояснено (один склад у Житомирі, вимог 99.99 % немає).</t>
+        </is>
+      </c>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="22" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 12 · Відновлення (Recovery)</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>1✗ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>Ціль обіцяє збереження «введених даних чекауту», а Опис і критерій перевіряють лише кошик — або додати перевірку чекауту, або прибрати з Цілі.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="n"/>
+      <c r="H56" s="22" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 13 · Інтернаціоналізації (i18n)</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>1✗ 2✗ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>«Суми з комами та крапками» — на demo немає поля введення сум (неможливо виконати); «відсутність жорстко закодованого тексту» в Описі не перевіряється. Твердження «demo лише англійською» неточне: на demo є перемикач мов (EN, DE, EL, ES, FR, NL, TR) — його можна використати для перевірки.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="n"/>
+      <c r="H57" s="22" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 14 · Локалізації (l10n)</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>1✗ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>Критерій «математика цін відповідає українським стандартам» неперевірюваний (як і слова-маркери в аудиті); формат індексу «5 цифр» не заданий у SRS — позначити як припущення; HALF_UP належить типу 5, не l10n.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="n"/>
+      <c r="H58" s="22" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 15 · Документації</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: у SRS D-10 — посібник користувача (Low), D-20 — README модуля з `mvn test` (Medium); у даних «розділ 5, D-10» плутає ID — виправити відповідність.</t>
+        </is>
+      </c>
+      <c r="G59" s="22" t="n"/>
+      <c r="H59" s="22" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 16 · Навантажувальне (Load)</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>Параметри відповідають P-20 (100 покупців, p95 ≤ 1 с, 10 хв); заборону на demo позначено, авторські значення позначено «потребує підтвердження замовником».</t>
+        </is>
+      </c>
+      <c r="G60" s="22" t="n"/>
+      <c r="H60" s="22" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 17 · Стресове (Stress)</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>Причину незастосовності названо (вимог до дефіциту ресурсів у SRS немає).</t>
+        </is>
+      </c>
+      <c r="G61" s="22" t="n"/>
+      <c r="H61" s="22" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 18 · Стрибкове (Spike)</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C62" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>Причина посилається на P-20 (рівномірне навантаження) — відповідає SRS.</t>
+        </is>
+      </c>
+      <c r="G62" s="22" t="n"/>
+      <c r="H62" s="22" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 19 · Порівняльне (Benchmarking)</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C63" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>Причину названо (немає попередньої версії й еталонів).</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="n"/>
+      <c r="H63" s="22" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 20 · Профілювання (Profiling)</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D64" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✗ 5✓</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>Причина спирається на «типовий монолітний вебзастосунок» — у SRS 1.0 архітектура інша (SPA + REST API + БД), твердження не підтверджено. Обґрунтувати природою продукту (напр., пороги вже в P-20, еталонів немає).</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="n"/>
+      <c r="H64" s="22" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 21 · Стабільності (Soak / Endurance)</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C65" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>Формулювання за рішенням КТ (SCRUM-58); покриття 30-хвилинним сценарієм типу 10 вказано.</t>
+        </is>
+      </c>
+      <c r="G65" s="22" t="n"/>
+      <c r="H65" s="22" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 22 · Витоків пам'яті (Memory Leaks)</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C66" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>За рішенням КТ (SCRUM-58): критерій 20 % позначено «потребує підтвердження замовником», пріоритет Low пояснено, межу (лише клієнтська частина) вказано.</t>
+        </is>
+      </c>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 23 · Вузьких місць (Bottleneck)</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C67" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>Редакційне: покриття типом 16, який на demo не запускається (ризик 1) — діє лише з локальним стендом.</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="n"/>
+      <c r="H67" s="22" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>План · тип 24 · Умов гонок (Race Conditions)</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>пройшло</t>
+        </is>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>Конкретний тест JUnit 5 (10 конкурентних викликів), пріоритет Medium пояснено, на demo не потрібен.</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="n"/>
+      <c r="H68" s="22" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>План · чернетка SCRUM-71 (файл plan.md від 11.10: розд. 5–6 + ID SRS 1.1)</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна А. (ІТ)</t>
+        </is>
+      </c>
+      <c r="C69" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr">
+        <is>
+          <t>розд. 5–6; різниця з main</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>не пройшло</t>
+        </is>
+      </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>Файл зібрано на старішій версії, ніж main: зникли ризики в Цілях і правки SCRUM-68–70 (типи 21/22, позначки замовника в 4/16/22). D-10/D-20 переплутані. У розд. 5 «розділ 9 SRS 1.1» (розділ 9 є в Каталозі, не в SRS), «артиклі»; не названо JMeter/k6, OWASP ZAP, IntelliJ IDEA, Google Forms, Postman Mock Server. Розд. 6: немає припущень, ризики без наслідку/пом'якшення/власника. Повернено ІТ із коментарем.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="n"/>
+      <c r="H69" s="22" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>SRS 1.1 · кожна правка має запис у журналі змін із № дефекту</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>очікує SRS 1.1</t>
+        </is>
+      </c>
+      <c r="F70" s="22" t="inlineStr">
+        <is>
+          <t>SRS 1.1 ще не створено (у docs/sprint2 її немає станом на 12.10.2026). Рядок заповнюю після появи файла; без файла «пройшло» не ставлю.</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="n"/>
+      <c r="H70" s="22" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>SRS 1.1 · ID не перенумеровані</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C71" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>очікує SRS 1.1</t>
+        </is>
+      </c>
+      <c r="F71" s="22" t="inlineStr">
+        <is>
+          <t>SRS 1.1 ще не створено (у docs/sprint2 її немає станом на 12.10.2026). Рядок заповнюю після появи файла; без файла «пройшло» не ставлю.</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="n"/>
+      <c r="H71" s="22" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>SRS 1.1 · незмінені вимоги дослівні</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Тимчак А. (ТА)</t>
+        </is>
+      </c>
+      <c r="C72" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ)</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>очікує SRS 1.1</t>
+        </is>
+      </c>
+      <c r="F72" s="22" t="inlineStr">
+        <is>
+          <t>SRS 1.1 ще не створено (у docs/sprint2 її немає станом на 12.10.2026). Рядок заповнюю після появи файла; без файла «пройшло» не ставлю.</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="n"/>
+      <c r="H72" s="22" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Пояснення</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>Умовні позначки: ✓ перевірено, ✗ не виконано, н/з — не застосовується (рядок відхилено).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Реєстр, пп.: 1 ID/локатор є в SRS 1.0; 2 цитата збігається зі SRS 1.0; 3 пункт чек-листа названо й доречний; 4 критерій головний; 5 виправлення готове; 6 виправлення не створює нового дефекту; 7 автор(и) зазначено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>План, пп.: 1 Ціль і Опис специфічні для ШопЛайн; 2 Опис виконуваний на demo або обмеження позначено; 3 названо інструменти й дані; 4 пріоритет і незастосовність пояснено; 5 рівні й типи в різних рядках.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Чек-листи — офіційні (методичка спринта 2, розд. 4.2–4.7). Рядки, де СМ — автор, рецензує КТ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Версії: Реєстр і План — main (92899b6, 12.10.2026). Рецензент СМ: Горбонос О., 12.10.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Виконуваність Описів на demo перевірено вибірково (API, редирект /account, форма реєстрації, перемикач мов); повний прогін сценаріїв не виконувався.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>«Виправлено» і «Повторне підтвердження» заповнюються лише після реальних правок авторів; для рядків, які пройшли з першого разу, повторне підтвердження не потрібне. Редакційні зауваження не змінюють результат, але мають бути враховані до SRS 1.1.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A81:F81"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -6416,17 +6416,17 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>не пройшло</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: варіант ТА («перенаправляє … на сторінку особистого кабінету (F-130)») суперечить F-110: після входу на кроці 2 «Sign in» покупець переходить на крок 3, а не в кабінет. Варіант СМ цю ситуацію враховує. Обрати варіант СМ і прибрати варіант ТА до SRS 1.1. Повернено ТА.</t>
         </is>
       </c>
       <c r="G5" s="22" t="n"/>
@@ -6459,17 +6459,17 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-30 дослівна; здійсненність — головний критерій (доставка залежить від стороннього провайдера). Редакційне: два варіанти (1 с / 5 с) — обрати один до SRS 1.1; час передачі вже позначено «потребує підтвердження замовником».</t>
         </is>
       </c>
       <c r="G6" s="22" t="n"/>
@@ -6604,17 +6604,17 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-60 дослівна; «схожі» допускає кілька тлумачень (п. 4). Одне спільне виправлення (підрядок без урахування регістру), звірене з demo.</t>
         </is>
       </c>
       <c r="G10" s="22" t="n"/>
@@ -6638,17 +6638,17 @@
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-90 дослівна; слова-маркери «миттєво», «без помилок» — тестопридатність. Редакційне: два варіанти (1 с / 2 с, різний спосіб спостереження) — обрати один до SRS 1.1; у варіанті ТА до «2 с» і тексту повідомлення додати «потребує підтвердження замовником».</t>
         </is>
       </c>
       <c r="G11" s="22" t="n"/>
@@ -6808,17 +6808,17 @@
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності).</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-140 дослівна; не задано формат, розмір вкладення і реакцію на недопустимий файл (пп. 4, 5). Редакційне: варіанти суперечать один одному (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ; максимальна довжина повідомлення лише у ТА) — обрати один до SRS 1.1.</t>
         </is>
       </c>
       <c r="G16" s="22" t="n"/>
@@ -8728,6 +8728,7 @@
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -204,6 +204,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6213,7 +6214,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="3" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -6282,7 +6283,7 @@
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>Коротка К. (КТ)</t>
+          <t>Дрєпіна А. (ІТ)</t>
         </is>
       </c>
       <c r="D2" s="22" t="inlineStr">
@@ -6292,17 +6293,17 @@
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>очікує ІТ</t>
         </is>
       </c>
       <c r="F2" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент.</t>
+          <t>СМ і КТ — співавтори рядка, тому рецензує ІТ (не автор цього рядка). Рецензія ІТ ще не внесена.</t>
         </is>
       </c>
       <c r="G2" s="22" t="n"/>
       <c r="H2" s="22" t="n"/>
-      <c r="J2" s="26" t="inlineStr">
+      <c r="J2" s="28" t="inlineStr">
         <is>
           <t>пройшло</t>
         </is>
@@ -6345,7 +6346,7 @@
       </c>
       <c r="G3" s="22" t="n"/>
       <c r="H3" s="22" t="n"/>
-      <c r="J3" s="26" t="inlineStr">
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>не пройшло</t>
         </is>
@@ -6388,7 +6389,7 @@
       </c>
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
-      <c r="J4" s="26" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>очікує КТ</t>
         </is>
@@ -6431,9 +6432,9 @@
       </c>
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
-      <c r="J5" s="26" t="inlineStr">
-        <is>
-          <t>очікує SRS 1.1</t>
+      <c r="J5" s="28" t="inlineStr">
+        <is>
+          <t>очікує ІТ</t>
         </is>
       </c>
       <c r="K5" s="26">
@@ -6474,13 +6475,13 @@
       </c>
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
-      <c r="J6" s="27" t="inlineStr">
-        <is>
-          <t>Разом</t>
+      <c r="J6" s="28" t="inlineStr">
+        <is>
+          <t>очікує SRS 1.1</t>
         </is>
       </c>
       <c r="K6" s="26">
-        <f>SUM(K2:K5)</f>
+        <f>COUNTIF($E$2:$E$72,J6)</f>
         <v/>
       </c>
     </row>
@@ -6497,7 +6498,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>Коротка К. (КТ)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6507,16 +6508,25 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>немає незалежного рецензента</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент (усі четверо автори; рядок розглянуто через «Спірні», рішення команди).</t>
+          <t>СМ — автор рядка. Незалежного рецензента в команді немає (усі четверо — автори); дефект підтверджено незалежним знаходженням чотирма аудиторами (§4.9) і рішенням команди.</t>
         </is>
       </c>
       <c r="G7" s="22" t="n"/>
       <c r="H7" s="22" t="n"/>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>немає незалежного рецензента</t>
+        </is>
+      </c>
+      <c r="K7" s="26">
+        <f>COUNTIF($E$2:$E$72,J7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
@@ -6551,6 +6561,15 @@
       </c>
       <c r="G8" s="22" t="n"/>
       <c r="H8" s="22" t="n"/>
+      <c r="J8" s="27" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="K8" s="26">
+        <f>SUM(K2:K7)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -6667,7 +6686,7 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>Коротка К. (КТ)</t>
+          <t>Дрєпіна А. (ІТ)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6677,12 +6696,12 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>очікує ІТ</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент.</t>
+          <t>СМ і КТ — співавтори рядка, тому рецензує ІТ (не автор цього рядка). Рецензія ІТ ще не внесена.</t>
         </is>
       </c>
       <c r="G12" s="22" t="n"/>
@@ -6701,7 +6720,7 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>Коротка К. (КТ)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6711,12 +6730,12 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>немає незалежного рецензента</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент (усі четверо автори; рядок розглянуто через «Спірні», рішення команди). Рядок переписано в PR #23 (SCRUM-56).</t>
+          <t>СМ — автор рядка. Незалежного рецензента в команді немає (усі четверо — автори); дефект підтверджено незалежним знаходженням чотирма аудиторами (§4.9) і рішенням команди. Рядок переписано в PR #23 (SCRUM-56).</t>
         </is>
       </c>
       <c r="G13" s="22" t="n"/>
@@ -6769,7 +6788,7 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>Коротка К. (КТ)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -6779,12 +6798,12 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>немає незалежного рецензента</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). КТ також співавтор — потрібен незалежний рецензент (усі четверо автори; рядок розглянуто через «Спірні», рішення команди). Рядок переписано в PR #23 (SCRUM-56).</t>
+          <t>СМ — автор рядка. Незалежного рецензента в команді немає (усі четверо — автори); дефект підтверджено незалежним знаходженням чотирма аудиторами (§4.9) і рішенням команди.</t>
         </is>
       </c>
       <c r="G15" s="22" t="n"/>
@@ -8760,7 +8779,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Чек-листи — офіційні (методичка спринта 2, розд. 4.2–4.7). Рядки, де СМ — автор, рецензує КТ.</t>
+          <t>Чек-листи — офіційні (методичка спринта 2, розд. 4.2–4.7). Рядки, де СМ — автор, рецензує КТ; якщо КТ також співавтор — ІТ; якщо автори всі четверо — незалежного рецензента немає (§4.9).</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -6477,7 +6477,7 @@
       <c r="H6" s="22" t="n"/>
       <c r="J6" s="28" t="inlineStr">
         <is>
-          <t>очікує SRS 1.1</t>
+          <t>очікує коміт ІТ</t>
         </is>
       </c>
       <c r="K6" s="26">
@@ -6520,7 +6520,7 @@
       <c r="H7" s="22" t="n"/>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>немає незалежного рецензента</t>
+          <t>очікує SRS 1.1</t>
         </is>
       </c>
       <c r="K7" s="26">
@@ -6561,13 +6561,13 @@
       </c>
       <c r="G8" s="22" t="n"/>
       <c r="H8" s="22" t="n"/>
-      <c r="J8" s="27" t="inlineStr">
-        <is>
-          <t>Разом</t>
+      <c r="J8" s="28" t="inlineStr">
+        <is>
+          <t>немає незалежного рецензента</t>
         </is>
       </c>
       <c r="K8" s="26">
-        <f>SUM(K2:K7)</f>
+        <f>COUNTIF($E$2:$E$72,J8)</f>
         <v/>
       </c>
     </row>
@@ -6604,6 +6604,15 @@
       </c>
       <c r="G9" s="22" t="n"/>
       <c r="H9" s="22" t="n"/>
+      <c r="J9" s="27" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="K9" s="28">
+        <f>SUM(K2:K8)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
@@ -7653,7 +7662,7 @@
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t>Ціль загальна («основні критичні функції») — не називає об'єкт і ризик ШопЛайн (напр., недоступний чекаут блокує всі подальші перевірки). Опис і дані конкретні.</t>
+          <t>Ціль загальна («основні критичні функції») — не називає об'єкт і ризик ШопЛайн (напр., недоступний чекаут блокує всі подальші перевірки). Опис і дані конкретні. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
         </is>
       </c>
       <c r="G40" s="22" t="n"/>
@@ -7687,7 +7696,7 @@
       </c>
       <c r="F41" s="22" t="inlineStr">
         <is>
-          <t>Ціль загальна; у «Інструменти / Дані» немає даних (обліковий запис, товари, промокод) — додати.</t>
+          <t>Ціль загальна; у «Інструменти / Дані» немає даних (обліковий запис, товари, промокод) — додати. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
         </is>
       </c>
       <c r="G41" s="22" t="n"/>
@@ -7755,7 +7764,7 @@
       </c>
       <c r="F43" s="22" t="inlineStr">
         <is>
-          <t>Ціль загальна (годиться для будь-якого продукту) — назвати об'єкт і ризик ШопЛайн. Опис конкретний, обмеження demo позначено.</t>
+          <t>Ціль загальна (годиться для будь-якого продукту) — назвати об'єкт і ризик ШопЛайн. Опис конкретний, обмеження demo позначено. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
         </is>
       </c>
       <c r="G43" s="22" t="n"/>
@@ -7891,7 +7900,7 @@
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Невиконуваний/суперечливий опис: пошук «Hammer» «через фільтр брендів» (Hammer — товар, не бренд); вибірка 10 учасників «на етапі UAT/альфа», а в Інструментах — «на Toolshop»; не вказано, де виконується. Вибірка 10 залежить від вибору варіанта U-10 у №25 (КТ: 5 учасників).</t>
+          <t>Невиконуваний/суперечливий опис: пошук «Hammer» «через фільтр брендів» (Hammer — товар, не бренд); вибірка 10 учасників «на етапі UAT/альфа», а в Інструментах — «на Toolshop»; не вказано, де виконується. Вибірка 10 залежить від вибору варіанта U-10 у №25 (КТ: 5 учасників). У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
         </is>
       </c>
       <c r="G47" s="22" t="n"/>
@@ -8197,7 +8206,7 @@
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t>Ціль обіцяє збереження «введених даних чекауту», а Опис і критерій перевіряють лише кошик — або додати перевірку чекауту, або прибрати з Цілі.</t>
+          <t>Ціль обіцяє збереження «введених даних чекауту», а Опис і критерій перевіряють лише кошик — або додати перевірку чекауту, або прибрати з Цілі. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
         </is>
       </c>
       <c r="G56" s="22" t="n"/>
@@ -8231,7 +8240,7 @@
       </c>
       <c r="F57" s="22" t="inlineStr">
         <is>
-          <t>«Суми з комами та крапками» — на demo немає поля введення сум (неможливо виконати); «відсутність жорстко закодованого тексту» в Описі не перевіряється. Твердження «demo лише англійською» неточне: на demo є перемикач мов (EN, DE, EL, ES, FR, NL, TR) — його можна використати для перевірки.</t>
+          <t>«Суми з комами та крапками» — на demo немає поля введення сум (неможливо виконати); «відсутність жорстко закодованого тексту» в Описі не перевіряється. Твердження «demo лише англійською» неточне: на demo є перемикач мов (EN, DE, EL, ES, FR, NL, TR) — його можна використати для перевірки. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
         </is>
       </c>
       <c r="G57" s="22" t="n"/>
@@ -8265,7 +8274,7 @@
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t>Критерій «математика цін відповідає українським стандартам» неперевірюваний (як і слова-маркери в аудиті); формат індексу «5 цифр» не заданий у SRS — позначити як припущення; HALF_UP належить типу 5, не l10n.</t>
+          <t>Критерій «математика цін відповідає українським стандартам» неперевірюваний (як і слова-маркери в аудиті); формат індексу «5 цифр» не заданий у SRS — позначити як припущення; HALF_UP належить типу 5, не l10n. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main. Тип стає «Ні» (15 застосовних / 9 незастосовних) — потрібне підтвердження КТ.</t>
         </is>
       </c>
       <c r="G58" s="22" t="n"/>
@@ -8469,7 +8478,7 @@
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t>Причина спирається на «типовий монолітний вебзастосунок» — у SRS 1.0 архітектура інша (SPA + REST API + БД), твердження не підтверджено. Обґрунтувати природою продукту (напр., пороги вже в P-20, еталонів немає).</t>
+          <t>Причина спирається на «типовий монолітний вебзастосунок» — у SRS 1.0 архітектура інша (SPA + REST API + БД), твердження не підтверджено. Обґрунтувати природою продукту (напр., пороги вже в P-20, еталонів немає). У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
         </is>
       </c>
       <c r="G64" s="22" t="n"/>
@@ -8614,7 +8623,7 @@
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>План · чернетка SCRUM-71 (файл plan.md від 11.10: розд. 5–6 + ID SRS 1.1)</t>
+          <t>План · SCRUM-71 (розд. 5–6, прив'язка до ID SRS 1.1): перевірено версії v1–v4, передано v5</t>
         </is>
       </c>
       <c r="B69" s="22" t="inlineStr">
@@ -8629,17 +8638,21 @@
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>розд. 5–6; різниця з main</t>
+          <t>розд. 5–6; різниця з main; пп. 1–5 плану</t>
         </is>
       </c>
       <c r="E69" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>очікує коміт ІТ</t>
         </is>
       </c>
       <c r="F69" s="22" t="inlineStr">
         <is>
-          <t>Файл зібрано на старішій версії, ніж main: зникли ризики в Цілях і правки SCRUM-68–70 (типи 21/22, позначки замовника в 4/16/22). D-10/D-20 переплутані. У розд. 5 «розділ 9 SRS 1.1» (розділ 9 є в Каталозі, не в SRS), «артиклі»; не названо JMeter/k6, OWASP ZAP, IntelliJ IDEA, Google Forms, Postman Mock Server. Розд. 6: немає припущень, ризики без наслідку/пом'якшення/власника. Повернено ІТ із коментарем.</t>
+          <t>v1 (11.10): не пройшло — основа старіша за main (зникли ризики в Цілях і правки SCRUM-68–70), D-10/D-20 переплутані, у розд. 5–6 бракувало інструментів, припущень, наслідку/пом'якшення/власника.
+v2: розд. 5–6 виправлено; типи 2, 3, 6, 14 з Описами слабшими за main.
+v3: виправлено типи 2, 3, 4, 6, 15, 16, 22; тип 14 посилався на валідацію індексу, якої немає в модулі.
+v4: пройшло з трьома правками (шкала 2.1 — прибрати l10n; причина «Ні» типу 14 — від продукту, не від demo; тип 13 — прибрати GUI-10). Тип 14 → «Ні» потребує підтвердження КТ (SCRUM-58). Відкрите: власник ризику 4 («СМ / ІТ») — рішення СМ.
+v5 (12.10.2026): правки внесено в файл за дорученням СМ (шкала 2.1, причина «Ні» типу 14, тип 13, заголовок типів), файл передано ІТ для коміту. Повторне підтвердження — після коміту й порівняння з main; станом на 12.10.2026 SCRUM-71 у репозиторії немає.</t>
         </is>
       </c>
       <c r="G69" s="22" t="n"/>
@@ -8747,7 +8760,6 @@
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -8651,7 +8651,7 @@
           <t>v1 (11.10): не пройшло — основа старіша за main (зникли ризики в Цілях і правки SCRUM-68–70), D-10/D-20 переплутані, у розд. 5–6 бракувало інструментів, припущень, наслідку/пом'якшення/власника.
 v2: розд. 5–6 виправлено; типи 2, 3, 6, 14 з Описами слабшими за main.
 v3: виправлено типи 2, 3, 4, 6, 15, 16, 22; тип 14 посилався на валідацію індексу, якої немає в модулі.
-v4: пройшло з трьома правками (шкала 2.1 — прибрати l10n; причина «Ні» типу 14 — від продукту, не від demo; тип 13 — прибрати GUI-10). Тип 14 → «Ні» потребує підтвердження КТ (SCRUM-58). Відкрите: власник ризику 4 («СМ / ІТ») — рішення СМ.
+v4: пройшло з трьома правками (шкала 2.1 — прибрати l10n; причина «Ні» типу 14 — від продукту, не від demo; тип 13 — прибрати GUI-10). Тип 14 → «Ні» потребує підтвердження КТ (SCRUM-58). Власник ризику 4 — СМ (рішення СМ, 12.10.2026); запис «СМ / ІТ» у плані лишається без змін.
 v5 (12.10.2026): правки внесено в файл за дорученням СМ (шкала 2.1, причина «Ні» типу 14, тип 13, заголовок типів), файл передано ІТ для коміту. Повторне підтвердження — після коміту й порівняння з main; станом на 12.10.2026 SCRUM-71 у репозиторії немає.</t>
         </is>
       </c>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -7657,16 +7657,24 @@
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t>Ціль загальна («основні критичні функції») — не називає об'єкт і ризик ШопЛайн (напр., недоступний чекаут блокує всі подальші перевірки). Опис і дані конкретні. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="n"/>
-      <c r="H40" s="22" t="n"/>
+          <t>Ціль загальна («основні критичні функції») — не називає об'єкт і ризик ШопЛайн (напр., недоступний чекаут блокує всі подальші перевірки). Опис і дані конкретні. Повторно перевірено у PR #27: виправлено.</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
@@ -7691,16 +7699,24 @@
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
         <is>
-          <t>Ціль загальна; у «Інструменти / Дані» немає даних (обліковий запис, товари, промокод) — додати. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="22" t="n"/>
+          <t>Ціль загальна; у «Інструменти / Дані» немає даних (обліковий запис, товари, промокод) — додати. Повторно перевірено у PR #27: виправлено.</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
@@ -7759,16 +7775,24 @@
       </c>
       <c r="E43" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F43" s="22" t="inlineStr">
         <is>
-          <t>Ціль загальна (годиться для будь-якого продукту) — назвати об'єкт і ризик ШопЛайн. Опис конкретний, обмеження demo позначено. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
-        </is>
-      </c>
-      <c r="G43" s="22" t="n"/>
-      <c r="H43" s="22" t="n"/>
+          <t>Ціль загальна (годиться для будь-якого продукту) — назвати об'єкт і ризик ШопЛайн. Опис конкретний, обмеження demo позначено. Повторно перевірено у PR #27: виправлено.</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
@@ -7895,16 +7919,24 @@
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F47" s="22" t="inlineStr">
         <is>
-          <t>Невиконуваний/суперечливий опис: пошук «Hammer» «через фільтр брендів» (Hammer — товар, не бренд); вибірка 10 учасників «на етапі UAT/альфа», а в Інструментах — «на Toolshop»; не вказано, де виконується. Вибірка 10 залежить від вибору варіанта U-10 у №25 (КТ: 5 учасників). У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="n"/>
-      <c r="H47" s="22" t="n"/>
+          <t>Невиконуваний/суперечливий опис: пошук «Hammer» «через фільтр брендів» (Hammer — товар, не бренд); вибірка 10 учасників «на етапі UAT/альфа», а в Інструментах — «на Toolshop»; не вказано, де виконується. Вибірка 10 залежить від вибору варіанта U-10 у №25 (КТ: 5 учасників). Повторно перевірено у PR #27: виправлено.</t>
+        </is>
+      </c>
+      <c r="G47" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
@@ -8201,16 +8233,24 @@
       </c>
       <c r="E56" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F56" s="22" t="inlineStr">
         <is>
-          <t>Ціль обіцяє збереження «введених даних чекауту», а Опис і критерій перевіряють лише кошик — або додати перевірку чекауту, або прибрати з Цілі. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
-        </is>
-      </c>
-      <c r="G56" s="22" t="n"/>
-      <c r="H56" s="22" t="n"/>
+          <t>Ціль обіцяє збереження «введених даних чекауту», а Опис і критерій перевіряють лише кошик — або додати перевірку чекауту, або прибрати з Цілі. Повторно перевірено у PR #27: виправлено.</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H56" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="22" t="inlineStr">
@@ -8235,16 +8275,24 @@
       </c>
       <c r="E57" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F57" s="22" t="inlineStr">
         <is>
-          <t>«Суми з комами та крапками» — на demo немає поля введення сум (неможливо виконати); «відсутність жорстко закодованого тексту» в Описі не перевіряється. Твердження «demo лише англійською» неточне: на demo є перемикач мов (EN, DE, EL, ES, FR, NL, TR) — його можна використати для перевірки. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="n"/>
-      <c r="H57" s="22" t="n"/>
+          <t>«Суми з комами та крапками» — на demo немає поля введення сум (неможливо виконати); «відсутність жорстко закодованого тексту» в Описі не перевіряється. Твердження «demo лише англійською» неточне: на demo є перемикач мов (EN, DE, EL, ES, FR, NL, TR) — його можна використати для перевірки. Повторно перевірено у PR #27: виправлено.</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H57" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
@@ -8269,16 +8317,24 @@
       </c>
       <c r="E58" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t>Критерій «математика цін відповідає українським стандартам» неперевірюваний (як і слова-маркери в аудиті); формат індексу «5 цифр» не заданий у SRS — позначити як припущення; HALF_UP належить типу 5, не l10n. У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main. Тип стає «Ні» (15 застосовних / 9 незастосовних) — потрібне підтвердження КТ.</t>
-        </is>
-      </c>
-      <c r="G58" s="22" t="n"/>
-      <c r="H58" s="22" t="n"/>
+          <t>Критерій «математика цін відповідає українським стандартам» неперевірюваний (як і слова-маркери в аудиті); формат індексу «5 цифр» не заданий у SRS — позначити як припущення; HALF_UP належить типу 5, не l10n. Повторно перевірено у PR #27: виправлено. Тип стає «Ні» (15 застосовних / 9 незастосовних): перевірка СМ пройшла, застосовність затверджує КТ (SCRUM-58) — підтвердження ще очікується.</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="22" t="inlineStr">
@@ -8473,16 +8529,24 @@
       </c>
       <c r="E64" s="22" t="inlineStr">
         <is>
-          <t>не пройшло</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F64" s="22" t="inlineStr">
         <is>
-          <t>Причина спирається на «типовий монолітний вебзастосунок» — у SRS 1.0 архітектура інша (SPA + REST API + БД), твердження не підтверджено. Обґрунтувати природою продукту (напр., пороги вже в P-20, еталонів немає). У v5 (SCRUM-71) виправлено; повторне підтвердження — після коміту ІТ і порівняння з main.</t>
-        </is>
-      </c>
-      <c r="G64" s="22" t="n"/>
-      <c r="H64" s="22" t="n"/>
+          <t>Причина спирається на «типовий монолітний вебзастосунок» — у SRS 1.0 архітектура інша (SPA + REST API + БД), твердження не підтверджено. Обґрунтувати природою продукту (напр., пороги вже в P-20, еталонів немає). Повторно перевірено у PR #27: виправлено.</t>
+        </is>
+      </c>
+      <c r="G64" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
@@ -8643,7 +8707,7 @@
       </c>
       <c r="E69" s="22" t="inlineStr">
         <is>
-          <t>очікує коміт ІТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F69" s="22" t="inlineStr">
@@ -8652,11 +8716,19 @@
 v2: розд. 5–6 виправлено; типи 2, 3, 6, 14 з Описами слабшими за main.
 v3: виправлено типи 2, 3, 4, 6, 15, 16, 22; тип 14 посилався на валідацію індексу, якої немає в модулі.
 v4: пройшло з трьома правками (шкала 2.1 — прибрати l10n; причина «Ні» типу 14 — від продукту, не від demo; тип 13 — прибрати GUI-10). Тип 14 → «Ні» потребує підтвердження КТ (SCRUM-58). Власник ризику 4 — СМ (рішення СМ, 12.10.2026); запис «СМ / ІТ» у плані лишається без змін.
-v5 (12.10.2026): правки внесено в файл за дорученням СМ (шкала 2.1, причина «Ні» типу 14, тип 13, заголовок типів), файл передано ІТ для коміту. Повторне підтвердження — після коміту й порівняння з main; станом на 12.10.2026 SCRUM-71 у репозиторії немає.</t>
-        </is>
-      </c>
-      <c r="G69" s="22" t="n"/>
-      <c r="H69" s="22" t="n"/>
+v5 = PR #27 (коміт cb56049, 12.10.2026): вміст збігається з перевіреним файлом (різниця лише в кінцевому переносі рядка); Описи типів — на рівні main, розд. 5–6 і правки 2.1/тип 13/тип 14 враховано. Залишається: merge PR #27 і підтвердження КТ щодо типу 14.</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr">
+        <is>
+          <t>12.10.2026 (ІТ, PR #27, коміт cb56049)</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>Горбонос Олександра (СМ), 12.10.2026 (PR #27, коміт cb56049; у main ще не змерджено)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
@@ -8760,6 +8832,7 @@
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
@@ -8798,7 +8871,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Версії: Реєстр і План — main (92899b6, 12.10.2026). Рецензент СМ: Горбонос О., 12.10.2026.</t>
+          <t>Версії: Реєстр і План — main (92899b6, 12.10.2026). Рецензент СМ: Горбонос О., 12.10.2026; план повторно — PR #27 (cb56049).</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -5674,7 +5674,7 @@
       </c>
       <c r="F35" s="22" t="inlineStr">
         <is>
-          <t>«… Результат містить ознаку придатності та причину відмови — по одній на кожну умову: INVALID_LENGTH (довжина коду поза межами 6–10 символів), EXPIRED (дата закінчення дії раніша за today), ALREADY_USED (одноразовий код уже використано), INVALID_PERCENT (для типу «відсоток» значення поза межами 1–50 включно), INVALID_AMOUNT (для типу «фіксована сума» значення не більше 0 або перевищує допустиму межу за BL-70); якщо не виконано кілька умов, повертається причина першої з них у цьому порядку; для придатного коду причина порожня.»</t>
+          <t>«… Результат містить ознаку придатності та причину відмови — по одній на кожну умову: INVALID_LENGTH (довжина коду поза межами 6–10 символів), EXPIRED (дата закінчення дії раніша за today), ALREADY_USED (одноразовий код уже використано), INVALID_PERCENT (для типу «відсоток» значення поза межами 1–50 включно), INVALID_AMOUNT (для типу «фіксована сума» значення не більше 0 або перевищує subtotal мінус знижка за обсяг (BL-50)); якщо не виконано кілька умов, повертається причина першої з них у цьому порядку; для придатного коду причина порожня.»</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>Переписано за рішенням команди (SCRUM-55, аркуш «Спірні»): обрано варіант з обмеженням у BL-70 замість BL-90; вартість доставки не зачіпається. Пов'язано з рядком №34 (причина INVALID_AMOUNT). Потребує підтвердження замовником.</t>
+          <t>Переписано за рішенням команди (SCRUM-55, аркуш «Спірні»): рішення дозволило два варіанти (обмеження в BL-70 або BL-90 лише з обрізанням до 0.00 і без доставки); ТА (Тимчак А.) обрала обмеження в BL-70; вартість доставки не зачіпається. Пов'язано з рядком №34 (причина INVALID_AMOUNT). Потребує підтвердження замовником.</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F3" s="22" t="inlineStr">
         <is>
-          <t>«… Обов'язкові поля: ім'я, прізвище, дата народження, країна, поштовий індекс, номер будинку, вулиця, місто, телефон, адреса електронної пошти, пароль; поле «область (штат)» необов'язкове; обов'язкові поля позначено у формі зірочкою.»</t>
+          <t>«… Обов'язкові поля: ім'я, прізвище, дата народження, країна, поштовий індекс, номер будинку, вулиця, місто, область (штат), телефон, адреса електронної пошти, пароль; обов'язкові поля позначено у формі зірочкою.»</t>
         </is>
       </c>
       <c r="G3" s="22" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="J3" s="22" t="inlineStr">
         <is>
-          <t>Інший дефект F-10 (зайнята e-mail) — окремий рядок. Потребує підтвердження замовником.</t>
+          <t>Інший дефект F-10 (зайнята e-mail) — окремий рядок. Після рецензії СМ (12.10.2026) «область (штат)» віднесено до обов'язкових полів: на demo поле state обов'язкове (aria-required=true у формі реєстрації), а F-110 (крок 3) включає область до адреси доставки. Перелік обов'язкових полів — потребує підтвердження замовником.</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -4117,8 +4117,7 @@
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>Варіант Горбонос О. (СМ): «Після успішного входу система перенаправляє покупця на сторінку особистого кабінету (/account); якщо вхід виконано на кроці «Sign in» оформлення замовлення (F-110) — на крок «Billing Address».»
-Варіант Тимчак А. (ТА): «Після успішного входу система перенаправляє покупця на сторінку особистого кабінету (F-130).»</t>
+          <t>Варіант Горбонос О. (СМ): «Після успішного входу система перенаправляє покупця на сторінку особистого кабінету (/account); якщо вхід виконано на кроці «Sign in» оформлення замовлення (F-110) — на крок «Billing Address».»</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -4138,7 +4137,7 @@
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>Обидва варіанти ведуть у кабінет; варіант Горбонос додатково описує вхід на кроці «Sign in» (F-110).</t>
+          <t>Після рецензії КТ (12.10.2026) залишено варіант Горбонос: варіант Тимчак («перенаправляє … на сторінку особистого кабінету (F-130)») суперечив F-110 — після входу на кроці «Sign in» покупець переходить на крок «Billing Address», а не в кабінет. Варіант Тимчак прибрано.</t>
         </is>
       </c>
       <c r="L5" s="23" t="inlineStr">

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -4197,7 +4197,7 @@
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>Варіанти різняться лише часом передачі листа (1 с / 5 с) — потребує підтвердження замовником.</t>
+          <t>Варіанти різняться лише часом передачі листа (1 с / 5 с) — потребує підтвердження замовником. До SRS 1.1 обрано варіант Горбонос (1 с): зберігає значення 1 с із SRS 1.0 і прибирає лише нездійсненну гарантію доставки до скриньки.</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
@@ -4466,7 +4466,7 @@
       <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Варіант Горбонос О. (СМ): «Натискання «Add to cart» не довше ніж за 1 с додає товар у кошик у вказаній кількості (позиція з'являється на кроці «Cart»), повідомлення про помилку не виводиться; повторне додавання того самого товару збільшує його кількість у кошику.» (Значення 1 с — потребує підтвердження замовником.)
-Варіант Тимчак А. (ТА): «Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с після натискання виводиться повідомлення «Product added to shopping cart.»; повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
+Варіант Тимчак А. (ТА): «Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с після натискання виводиться повідомлення «Product added to shopping cart.» (час 2 с і текст повідомлення — потребує підтвердження замовником); повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="J11" s="22" t="inlineStr">
         <is>
-          <t>Варіанти різняться часом (1 с / 2 с) і способом спостереження — потребує підтвердження замовником.</t>
+          <t>Варіанти різняться часом (1 с / 2 с) і способом спостереження — потребує підтвердження замовником. До SRS 1.1 обрано варіант Тимчак: результат спостерігається на сторінці товару (повідомлення, звірене з demo) без переходу в кошик і пов'язаний з BL-20.</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>Варіанти різняться форматами й розміром файла (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ); максимальну довжину повідомлення пропонує лише Тимчак. Потребує підтвердження замовником.</t>
+          <t>Варіанти різняться форматами й розміром файла (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ); максимальну довжину повідомлення пропонує лише Тимчак. Потребує підтвердження замовником. До SRS 1.1 обрано варіант Тимчак: лише він задає максимальну довжину повідомлення, відсутність якої названо в описі дефекту; формат .txt відповідає demo.</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>Варіанти суперечать один одному (не менше 1200×1200 / до 800×800) — потребує підтвердження замовником.</t>
+          <t>Варіанти суперечать один одному (не менше 1200×1200 / до 800×800) — потребує підтвердження замовником. До SRS 1.1 обрано варіант Коротка (вибір ТА): зберігає намір замовника (мінімальна роздільна здатність) і задає перевірюваний час для картки за 10 Мбіт/с.</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>Варіанти різняться значеннями (3 с у 95 % при 10 Мбіт/с / 2 с і FCP 1 с при 15 Мбіт/с) — потребує підтвердження замовником.</t>
+          <t>Варіанти різняться значеннями (3 с у 95 % при 10 Мбіт/с / 2 с і FCP 1 с при 15 Мбіт/с) — потребує підтвердження замовником. До SRS 1.1 обрано варіант Коротка (вибір ТА): задано інструмент, кількість вимірювань і частку (95 %), тож результат тесту однозначний.</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>Варіанти частково перетинаються (bcrypt, HTTPS) і можуть бути об'єднані. Коротка: «не містить вразливостей» порушує й здійсненність, головний критерій — тестопридатність. Перелік заходів — потребує підтвердження замовником.</t>
+          <t>Варіанти частково перетинаються (bcrypt, HTTPS) і можуть бути об'єднані. Коротка: «не містить вразливостей» порушує й здійсненність, головний критерій — тестопридатність. Перелік заходів — потребує підтвердження замовником. До SRS 1.1 варіанти об'єднано (вибір ТА): bcrypt, лише HTTPS із перенаправленням HTTP, код 403 для даних іншого покупця (Коротка); TLS 1.3 і відсутність вразливостей Critical/High за скануванням на локальному тестовому стенді (Дрєпіна) — потребує підтвердження замовником.</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="J26" s="22" t="inlineStr">
         <is>
-          <t>Варіанти різняться методикою (4 з 5 учасників / 90 % з 10 респондентів) — потребує підтвердження замовником.</t>
+          <t>Варіанти різняться методикою (4 з 5 учасників / 90 % з 10 респондентів) — потребує підтвердження замовником. До SRS 1.1 обрано варіант Дрєпіна (вибір ТА): його вже використовує план тестування (тип 3, 10 учасників).</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -4374,7 +4374,7 @@
       </c>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>Класифікація: аналогічний дефект GUI-70 (текст повідомлення не задано) віднесено до однозначності — узгодити один критерій для обох рядків.</t>
+          <t>Відхилено після обговорення (аркуш «Спірні», модерація КТ, 08.10.2026): наявність повідомлення про відсутність товарів перевіряється однозначно, точний текст — деталь дизайну; рішення однакове з №20.</t>
         </is>
       </c>
       <c r="L9" s="23" t="n"/>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>Варіанти різняться форматами й розміром файла (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ); максимальну довжину повідомлення пропонує лише Тимчак. Потребує підтвердження замовником. До SRS 1.1 обрано варіант Тимчак: лише він задає максимальну довжину повідомлення, відсутність якої названо в описі дефекту; формат .txt відповідає demo.</t>
+          <t>Варіанти різняться форматами й розміром файла (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ); максимальну довжину повідомлення пропонує лише Тимчак. Потребує підтвердження замовником. До SRS 1.1 обрано варіант Тимчак: лише він задає максимальну довжину повідомлення, відсутність якої названо в описі дефекту.</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="J17" s="22" t="inlineStr">
         <is>
-          <t>Сумнівний: автор вказав середню впевненість; другий аудитор розділу 4 (Дрєпіна) не знайшов. Перелік мов звірено з demo 01.10.2026.</t>
+          <t>Відхилено після обговорення (аркуш «Спірні», модерація КТ, 08.10.2026): перелік мов узято з demo, а не зі SRS. Винесено питанням замовнику на демо: які мови підтримує перемикач, чи є українська, яка мова за замовчуванням.</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>Сумнівний: автор вказав середню впевненість; другий аудитор розділу 4 (Дрєпіна) не знайшов. Класифікація: аналогічний дефект F-50 віднесено до тестопридатності. Текст — потребує підтвердження замовником.</t>
+          <t>Відхилено після обговорення (аркуш «Спірні», модерація КТ, 08.10.2026): наявність повідомлення замість таблиці перевіряється однозначно, точний текст — деталь дизайну; рішення однакове з №8.</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J29" s="22" t="inlineStr">
         <is>
-          <t>Інший дефект BL-10 (параметр name) — окремий рядок.</t>
+          <t>Інший дефект BL-10 (параметр name) — окремий рядок. Виправлення №28 і №29 правлять одне речення BL-10 — у SRS 1.1 вносяться одним записом, щоб не втратити «name».</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,11 @@
           <t>audit_tymchak №15</t>
         </is>
       </c>
-      <c r="J30" s="22" t="n"/>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>Правило «name — непорожній рядок» — нова вимога, потребує підтвердження замовником. Виправлення №28 і №29 правлять одне речення BL-10 — у SRS 1.1 вносяться одним записом.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="n">
@@ -5547,7 +5551,7 @@
       </c>
       <c r="J32" s="22" t="inlineStr">
         <is>
-          <t>Класифікація: п. 4 перевіряє формат ID, а не складеність вимоги; другий аудитор розділу 5 (Дрєпіна) не знайшов.</t>
+          <t>Відхилено після обговорення (аркуш «Спірні», модерація КТ, 08.10.2026): п. 4 чек-листа простежуваності не порушено — формат ID із кроком 10 дозволяє розділити вимогу без впливу на решту ID.</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5599,11 @@
           <t>audit_tymchak №18</t>
         </is>
       </c>
-      <c r="J33" s="22" t="n"/>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>Відхилено після обговорення (аркуш «Спірні», модерація КТ, 08.10.2026): «від N» — нижня межа включно, застосовується лише найвищий рівень (US-06); єдина інтерпретація існує.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="n">
@@ -5743,7 +5751,7 @@
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>Виправлення збігаються (перевірка лише в межах ШопЛайн, IllegalArgumentException).</t>
+          <t>Виправлення збігаються (перевірка лише в межах ШопЛайн, IllegalArgumentException). Виправлення звужує правило замовника (перевірка лише в межах ШопЛайн) — потребує підтвердження замовником.</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -6288,17 +6288,17 @@
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
-          <t>очікує ІТ</t>
+          <t>не пройшло</t>
         </is>
       </c>
       <c r="F2" s="22" t="inlineStr">
         <is>
-          <t>СМ і КТ — співавтори рядка, тому рецензує ІТ (не автор цього рядка). Рецензія ІТ ще не внесена.</t>
+          <t>Рецензія ІТ (Дрєпіна А.), 12.10.2026, звірено зі SRS 1.0: цитата з 2.2 дослівна («…на настільних операційних системах; мінімальна роздільна здатність вікна 1280×800»); вимога про 375 px і 44×44 є в розд. 6 без ID, між U-20 і D-10; суперечність реальна, головний критерій — несуперечливість (п. 2); автори СМ і КТ зазначені. Два варіанти не узгоджені: СМ лише знижує мінімальну ширину вікна до 375 px (лишає «настільні ОС» і 1280×800 як основний розмір; позначено «потребує підтвердження замовником»); КТ додає Chrome для Android 120+ і Safari для iOS 17+ та прибирає 1280×800. Варіант КТ створює нову вимогу, якої немає в SRS 1.0 (мобільні браузери й версії; у 1.2 поза обсягом лише мобільний застосунок), і без позначки «потребує підтвердження замовником» у тексті виправлення (у Примітці рядка вона є) — п. 6 ✗. Залишити варіант СМ як мінімальний; мобільні браузери — окремим питанням замовнику. Редакційне: 44×44 px (сенсорне керування) узгодити з формулюванням «настільні ОС». Повернено авторам: ТА залишає в реєстрі лише варіант СМ.</t>
         </is>
       </c>
       <c r="G2" s="22" t="n"/>
@@ -6700,17 +6700,17 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>очікує ІТ</t>
+          <t>не пройшло</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>СМ і КТ — співавтори рядка, тому рецензує ІТ (не автор цього рядка). Рецензія ІТ ще не внесена.</t>
+          <t>Рецензія ІТ (Дрєпіна А.), 12.10.2026, звірено зі SRS 1.0: цитата F-100 дослівна («Обмеження на кількість одиниць у рядку визначає вимога BL-25.»); у розд. 5 є BL-10…BL-80 з кроком 10, BL-25 немає (п. 3 чек-листа повноти доречний); автори СМ, КТ і ТА зазначені. Два варіанти не узгоджені: КТ/ТА називають BL-10, BL-20 і BL-40; СМ — лише BL-40. Варіант КТ/ТА правильний і повний: BL-10 — qty від 1 до 99 при додаванні, BL-20 — результуюча кількість рядка не більша за 99, BL-40 — changeQty від 1 до 99. Варіант СМ неповний — п. 6 ✗: посилання лише на BL-40 лишає поза межами правила BL-10 і BL-20 (додавання та повторне додавання). Залишити варіант КТ/ТА (BL-10, BL-20 і BL-40); варіант СМ прибрати, з нього можна взяти лише слова «ціле число від 1 до 99 включно» (як у BL-10). Повернено авторам: ТА залишає в реєстрі лише варіант КТ/ТА.</t>
         </is>
       </c>
       <c r="G12" s="22" t="n"/>
@@ -8832,7 +8832,6 @@
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -7,16 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Розподіл розділів" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_horbonos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_korotka" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_drepina" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_tymchak" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реєстр" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спірні" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Про файл" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Розподіл розділів" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_horbonos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_korotka" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_drepina" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_tymchak" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реєстр" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спірні" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Реєстр'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Реєстр'!$A$1:$J$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -198,6 +199,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -575,6 +579,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Значення</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Артефакт</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Реєстр дефектів вимог SRS 1.0 (аудит розділів, зведений реєстр, спірні рядки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Продукт</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>№1 «ШопЛайн»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Спринт</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>2 (1–15 жовтня 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Автори</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Горбонос О. (СМ), Коротка К. (КТ), Дрєпіна А. (ІТ), Тимчак А. (ТА)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -728,7 +822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1224,7 +1318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2078,7 +2172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2774,7 +2868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3827,7 +3921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4524,8 +4618,7 @@
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>Варіант Коротка К. (КТ), Тимчак А. (ТА): «Обмеження на кількість одиниць у рядку (від 1 до 99) визначають вимоги BL-10, BL-20 і BL-40.»
-Варіант Горбонос О. (СМ): «Обмеження на кількість одиниць у рядку (ціле число від 1 до 99 включно) визначає вимога BL-40.»</t>
+          <t>Варіант Коротка К. (КТ), Тимчак А. (ТА): «Обмеження на кількість одиниць у рядку (від 1 до 99) визначають вимоги BL-10, BL-20 і BL-40.»</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -4543,7 +4636,11 @@
           <t>audit_horbonos №3; audit_korotka №17; audit_tymchak №10</t>
         </is>
       </c>
-      <c r="J12" s="22" t="n"/>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Для SRS 1.1 обрано варіант КТ/ТА (посилання на всі вимоги, що задають межі кількості: BL-10, BL-20, BL-40); варіант СМ прибрано за рецензією SCRUM-59.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="n">
@@ -5819,7 +5916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -4033,8 +4033,7 @@
       </c>
       <c r="F2" s="22" t="inlineStr">
         <is>
-          <t>Варіант Горбонос О. (СМ): У 2.2: «Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах; підтримувані розміри вікна — від 375 пікселів у ширину (мобільний вигляд інтерфейсу) і більше, основний настільний розмір — 1280×800.» (Мінімальну ширину 375 px узято з розділу 6 — потребує підтвердження замовником.)
-Варіант Коротка К. (КТ): 2.2: «Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах, Chrome для Android 120 і новіші, Safari для iOS 17 і новіші; мінімальна ширина вікна — 375 пікселів.»</t>
+          <t>Варіант Горбонос О. (СМ): У 2.2: «Підтримувані браузери: Chrome 120 і новіші, Firefox 115 і новіші на настільних операційних системах; підтримувані розміри вікна — від 375 пікселів у ширину (мобільний вигляд інтерфейсу) і більше, основний настільний розмір — 1280×800.» (Мінімальну ширину 375 px узято з розділу 6 — потребує підтвердження замовником.)</t>
         </is>
       </c>
       <c r="G2" s="22" t="inlineStr">
@@ -4054,7 +4053,7 @@
       </c>
       <c r="J2" s="22" t="inlineStr">
         <is>
-          <t>Відсутність ID у вимозі розд. 6 — окремий рядок (див. «розд. 6, між U-20 і D-10»). Варіанти виправлення різняться (мобільні браузери) — потребує підтвердження замовником.</t>
+          <t>Відсутність ID у вимозі розд. 6 — окремий рядок (див. «розд. 6, між U-20 і D-10»). Для SRS 1.1 обрано мінімальний варіант СМ (ширина від 375 px, основний розмір 1280×800) за рекомендацією рецензії ІТ: вихідні вимоги не називають мобільних браузерів і їхніх версій, тож вносити їх без замовника не можна. Варіант КТ (Chrome для Android 120+, Safari для iOS 17+) винесено питанням замовнику на демо — потребує підтвердження замовником.</t>
         </is>
       </c>
       <c r="L2" s="23" t="inlineStr">

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -6402,17 +6402,17 @@
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
-          <t>очікує ІТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F2" s="22" t="inlineStr">
         <is>
-          <t>Рецензія ІТ (Дрєпіна А.), 12.10.2026, звірено зі SRS 1.0: цитата з 2.2 дослівна («…на настільних операційних системах; мінімальна роздільна здатність вікна 1280×800»); вимога про 375 px і 44×44 є в розд. 6 без ID, між U-20 і D-10; суперечність реальна, головний критерій — несуперечливість (п. 2); автори СМ і КТ зазначені. Два варіанти не узгоджені: СМ лише знижує мінімальну ширину вікна до 375 px (лишає «настільні ОС» і 1280×800 як основний розмір; позначено «потребує підтвердження замовником»); КТ додає Chrome для Android 120+ і Safari для iOS 17+ та прибирає 1280×800. Варіант КТ створює нову вимогу, якої немає в SRS 1.0 (мобільні браузери й версії; у 1.2 поза обсягом лише мобільний застосунок), і без позначки «потребує підтвердження замовником» у тексті виправлення (у Примітці рядка вона є) — п. 6 ✗. Залишити варіант СМ як мінімальний; мобільні браузери — окремим питанням замовнику. Редакційне: 44×44 px (сенсорне керування) узгодити з формулюванням «настільні ОС». Повернено авторам: ТА залишає в реєстрі лише варіант СМ. Виправлено в main (PR #28) 13.10.2026: обрано варіант А (ширина від 375 px, основний розмір 1280×800), мобільні браузери винесено питанням замовнику; очікує повторного підтвердження ІТ (Дрєпіна А.).</t>
+          <t>Рецензія ІТ (Дрєпіна А.), 12.10.2026, звірено зі SRS 1.0: цитата з 2.2 дослівна («…на настільних операційних системах; мінімальна роздільна здатність вікна 1280×800»); вимога про 375 px і 44×44 є в розд. 6 без ID, між U-20 і D-10; суперечність реальна, головний критерій — несуперечливість (п. 2); автори СМ і КТ зазначені. Два варіанти не узгоджені: СМ лише знижує мінімальну ширину вікна до 375 px (лишає «настільні ОС» і 1280×800 як основний розмір; позначено «потребує підтвердження замовником»); КТ додає Chrome для Android 120+ і Safari для iOS 17+ та прибирає 1280×800. Варіант КТ створює нову вимогу, якої немає в SRS 1.0 (мобільні браузери й версії; у 1.2 поза обсягом лише мобільний застосунок), і без позначки «потребує підтвердження замовником» у тексті виправлення (у Примітці рядка вона є) — п. 6 ✗. Залишити варіант СМ як мінімальний; мобільні браузери — окремим питанням замовнику. Редакційне: 44×44 px (сенсорне керування) узгодити з формулюванням «настільні ОС». Повернено авторам: ТА залишає в реєстрі лише варіант СМ. Виправлено в main (PR #28) 13.10.2026: обрано варіант А (ширина від 375 px, основний розмір 1280×800), мобільні браузери винесено питанням замовнику; Повторно підтверджено ІТ (Дрєпіна А.) 13.10.2026.</t>
         </is>
       </c>
       <c r="G2" s="22" t="inlineStr">
@@ -6420,7 +6420,11 @@
           <t>13.10.2026 (ТА, PR #28)</t>
         </is>
       </c>
-      <c r="H2" s="22" t="n"/>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна Анастасія (ІТ), 13.10.2026</t>
+        </is>
+      </c>
       <c r="J2" s="27" t="inlineStr">
         <is>
           <t>пройшло</t>
@@ -6543,17 +6547,17 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: варіант ТА («перенаправляє … на сторінку особистого кабінету (F-130)») суперечить F-110: після входу на кроці 2 «Sign in» покупець переходить на крок 3, а не в кабінет. Варіант СМ цю ситуацію враховує. Обрати варіант СМ і прибрати варіант ТА до SRS 1.1. Повернено ТА. Виправлено в main (PR #28) 13.10.2026: варіант ТА прибрано; очікує повторного підтвердження КТ.</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: варіант ТА («перенаправляє … на сторінку особистого кабінету (F-130)») суперечить F-110: після входу на кроці 2 «Sign in» покупець переходить на крок 3, а не в кабінет. Варіант СМ цю ситуацію враховує. Обрати варіант СМ і прибрати варіант ТА до SRS 1.1. Повернено ТА. Виправлено в main (PR #28) 13.10.2026: варіант ТА прибрано; Повторно підтверджено КТ (Коротка К.) 13.10.2026.</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -6561,7 +6565,11 @@
           <t>13.10.2026 (ТА, PR #28)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="n"/>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>Коротка Ксенія (КТ), 13.10.2026</t>
+        </is>
+      </c>
       <c r="J5" s="27" t="inlineStr">
         <is>
           <t>очікує ІТ</t>
@@ -6600,7 +6608,7 @@
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-30 дослівна; здійсненність — головний критерій (доставка залежить від стороннього провайдера). Редакційне: два варіанти (1 с / 5 с) — обрати один до SRS 1.1; час передачі вже позначено «потребує підтвердження замовником». Редакційну правку (вибір варіанта) внесено в main (PR #28) 13.10.2026; повторне підтвердження КТ очікується.</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-30 дослівна; здійсненність — головний критерій (доставка залежить від стороннього провайдера). Редакційне: два варіанти (1 с / 5 с) — обрати один до SRS 1.1; час передачі вже позначено «потребує підтвердження замовником». Редакційну правку (вибір варіанта) внесено в main (PR #28) 13.10.2026; повторно підтверджено КТ (Коротка К.) 13.10.2026.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -6608,7 +6616,11 @@
           <t>13.10.2026 (ТА, PR #28)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="n"/>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Коротка Ксенія (КТ), 13.10.2026</t>
+        </is>
+      </c>
       <c r="J6" s="27" t="inlineStr">
         <is>
           <t>немає незалежного рецензента</t>
@@ -6806,7 +6818,7 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-90 дослівна; слова-маркери «миттєво», «без помилок» — тестопридатність. Редакційне: два варіанти (1 с / 2 с, різний спосіб спостереження) — обрати один до SRS 1.1; у варіанті ТА до «2 с» і тексту повідомлення додати «потребує підтвердження замовником». Редакційну правку (вибір варіанта) внесено в main (PR #28) 13.10.2026; повторне підтвердження КТ очікується.</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-90 дослівна; слова-маркери «миттєво», «без помилок» — тестопридатність. Редакційне: два варіанти (1 с / 2 с, різний спосіб спостереження) — обрати один до SRS 1.1; у варіанті ТА до «2 с» і тексту повідомлення додати «потребує підтвердження замовником». Редакційну правку (вибір варіанта) внесено в main (PR #28) 13.10.2026; повторно підтверджено КТ (Коротка К.) 13.10.2026.</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -6814,7 +6826,11 @@
           <t>13.10.2026 (ТА, PR #28)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="n"/>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>Коротка Ксенія (КТ), 13.10.2026</t>
+        </is>
+      </c>
       <c r="J11" s="31" t="n"/>
       <c r="K11" s="31" t="n"/>
     </row>
@@ -6836,17 +6852,17 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✗ 7✓</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓ 6✓ 7✓</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>очікує ІТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>Рецензія ІТ (Дрєпіна А.), 12.10.2026, звірено зі SRS 1.0: цитата F-100 дослівна («Обмеження на кількість одиниць у рядку визначає вимога BL-25.»); у розд. 5 є BL-10…BL-80 з кроком 10, BL-25 немає (п. 3 чек-листа повноти доречний); автори СМ, КТ і ТА зазначені. Два варіанти не узгоджені: КТ/ТА називають BL-10, BL-20 і BL-40; СМ — лише BL-40. Варіант КТ/ТА правильний і повний: BL-10 — qty від 1 до 99 при додаванні, BL-20 — результуюча кількість рядка не більша за 99, BL-40 — changeQty від 1 до 99. Варіант СМ неповний — п. 6 ✗: посилання лише на BL-40 лишає поза межами правила BL-10 і BL-20 (додавання та повторне додавання). Залишити варіант КТ/ТА (BL-10, BL-20 і BL-40); варіант СМ прибрати, з нього можна взяти лише слова «ціле число від 1 до 99 включно» (як у BL-10). Повернено авторам: ТА залишає в реєстрі лише варіант КТ/ТА. Виправлено в main (PR #28) 13.10.2026: лишено варіант КТ/ТА, варіант СМ прибрано; очікує повторного підтвердження ІТ (Дрєпіна А.).</t>
+          <t>Рецензія ІТ (Дрєпіна А.), 12.10.2026, звірено зі SRS 1.0: цитата F-100 дослівна («Обмеження на кількість одиниць у рядку визначає вимога BL-25.»); у розд. 5 є BL-10…BL-80 з кроком 10, BL-25 немає (п. 3 чек-листа повноти доречний); автори СМ, КТ і ТА зазначені. Два варіанти не узгоджені: КТ/ТА називають BL-10, BL-20 і BL-40; СМ — лише BL-40. Варіант КТ/ТА правильний і повний: BL-10 — qty від 1 до 99 при додаванні, BL-20 — результуюча кількість рядка не більша за 99, BL-40 — changeQty від 1 до 99. Варіант СМ неповний — п. 6 ✗: посилання лише на BL-40 лишає поза межами правила BL-10 і BL-20 (додавання та повторне додавання). Залишити варіант КТ/ТА (BL-10, BL-20 і BL-40); варіант СМ прибрати, з нього можна взяти лише слова «ціле число від 1 до 99 включно» (як у BL-10). Повернено авторам: ТА залишає в реєстрі лише варіант КТ/ТА. Виправлено в main (PR #28) 13.10.2026: лишено варіант КТ/ТА, варіант СМ прибрано; Повторно підтверджено ІТ (Дрєпіна А.) 13.10.2026.</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -6854,7 +6870,11 @@
           <t>13.10.2026 (ТА, PR #28)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="n"/>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Дрєпіна Анастасія (ІТ), 13.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
@@ -6994,7 +7014,7 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-140 дослівна; не задано формат, розмір вкладення і реакцію на недопустимий файл (пп. 4, 5). Редакційне: варіанти суперечать один одному (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ; максимальна довжина повідомлення лише у ТА) — обрати один до SRS 1.1. Редакційну правку (вибір варіанта) внесено в main (PR #28) 13.10.2026; повторне підтвердження КТ очікується.</t>
+          <t>СМ — автор рядка, рецензує КТ (правило незалежності). Рецензія КТ (Коротка К.), 12.10.2026: цитата F-140 дослівна; не задано формат, розмір вкладення і реакцію на недопустимий файл (пп. 4, 5). Редакційне: варіанти суперечать один одному (PDF/PNG/JPG/TXT до 5 МБ / .txt до 500 КБ; максимальна довжина повідомлення лише у ТА) — обрати один до SRS 1.1. Редакційну правку (вибір варіанта) внесено в main (PR #28) 13.10.2026; повторно підтверджено КТ (Коротка К.) 13.10.2026.</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -7002,7 +7022,11 @@
           <t>13.10.2026 (ТА, PR #28)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="n"/>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>Коротка Ксенія (КТ), 13.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -8578,7 +8602,7 @@
       </c>
       <c r="F58" s="22" t="inlineStr">
         <is>
-          <t>Критерій «математика цін відповідає українським стандартам» неперевірюваний (як і слова-маркери в аудиті); формат індексу «5 цифр» не заданий у SRS — позначити як припущення; HALF_UP належить типу 5, не l10n. Повторно перевірено у PR #27: виправлено. Тип стає «Ні» (15 застосовних / 9 незастосовних): перевірка СМ пройшла, застосовність затверджує КТ (SCRUM-58) — підтвердження ще очікується.</t>
+          <t>Критерій «математика цін відповідає українським стандартам» неперевірюваний (як і слова-маркери в аудиті); формат індексу «5 цифр» не заданий у SRS — позначити як припущення; HALF_UP належить типу 5, не l10n. Повторно перевірено у PR #27: виправлено. Тип стає «Ні» (15 застосовних / 9 незастосовних): перевірка СМ пройшла, застосовність «Ні» підтверджено КТ (SCRUM-58) 13.10.2026.</t>
         </is>
       </c>
       <c r="G58" s="22" t="inlineStr">
@@ -8972,7 +8996,7 @@
 v2: розд. 5–6 виправлено; типи 2, 3, 6, 14 з Описами слабшими за main.
 v3: виправлено типи 2, 3, 4, 6, 15, 16, 22; тип 14 посилався на валідацію індексу, якої немає в модулі.
 v4: пройшло з трьома правками (шкала 2.1 — прибрати l10n; причина «Ні» типу 14 — від продукту, не від demo; тип 13 — прибрати GUI-10). Тип 14 → «Ні» потребує підтвердження КТ (SCRUM-58). Власник ризику 4 — СМ (рішення СМ, 12.10.2026); запис «СМ / ІТ» у плані лишається без змін.
-v5 = PR #27 (коміт cb56049, 12.10.2026): вміст збігається з перевіреним файлом (різниця лише в кінцевому переносі рядка); Описи типів — на рівні main, розд. 5–6 і правки 2.1/тип 13/тип 14 враховано. PR #27 змерджено в main (ed81b44). Залишається підтвердження КТ щодо типу 14 (застосовність затверджує КТ, SCRUM-58).</t>
+v5 = PR #27 (коміт cb56049, 12.10.2026): вміст збігається з перевіреним файлом (різниця лише в кінцевому переносі рядка); Описи типів — на рівні main, розд. 5–6 і правки 2.1/тип 13/тип 14 враховано. PR #27 змерджено в main (ed81b44). Застосовність типу 14 «Ні» підтверджено КТ (SCRUM-58) 13.10.2026.</t>
         </is>
       </c>
       <c r="G69" s="22" t="inlineStr">
@@ -9088,7 +9112,6 @@
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -4278,8 +4278,8 @@
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>Варіант Горбонос О. (СМ): «Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому сервісу не довше ніж за 1 секунду; час доставки до скриньки залежить від поштового провайдера одержувача і не гарантується.»
-Варіант Тимчак А. (ТА): «Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому серверу ШопЛайн не пізніше ніж за 5 с; час доставки до скриньки одержувача залежить від його поштового провайдера і не гарантується.»</t>
+          <t>ОБРАНО для SRS 1.1 — Варіант Горбонос О. (СМ): «Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому сервісу не довше ніж за 1 секунду; час доставки до скриньки залежить від поштового провайдера одержувача і не гарантується.»
+Не внесено — Варіант Тимчак А. (ТА): «Після надсилання форми система формує лист із посиланням для встановлення нового пароля і передає його поштовому серверу ШопЛайн не пізніше ніж за 5 с; час доставки до скриньки одержувача залежить від його поштового провайдера і не гарантується.»</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -4567,8 +4567,8 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>Варіант Горбонос О. (СМ): «Натискання «Add to cart» не довше ніж за 1 с додає товар у кошик у вказаній кількості (позиція з'являється на кроці «Cart»), повідомлення про помилку не виводиться; повторне додавання того самого товару збільшує його кількість у кошику.» (Значення 1 с — потребує підтвердження замовником.)
-Варіант Тимчак А. (ТА): «Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с після натискання виводиться повідомлення «Product added to shopping cart.» (час 2 с і текст повідомлення — потребує підтвердження замовником); повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
+          <t>Не внесено — Варіант Горбонос О. (СМ): «Натискання «Add to cart» не довше ніж за 1 с додає товар у кошик у вказаній кількості (позиція з'являється на кроці «Cart»), повідомлення про помилку не виводиться; повторне додавання того самого товару збільшує його кількість у кошику.» (Значення 1 с — потребує підтвердження замовником.)
+ОБРАНО для SRS 1.1 — Варіант Тимчак А. (ТА): «Натискання «Add to cart» додає товар у кошик у кількості з поля «Quantity»; не пізніше ніж за 2 с після натискання виводиться повідомлення «Product added to shopping cart.» (час 2 с і текст повідомлення — потребує підтвердження замовником); повторне додавання того самого товару збільшує кількість у наявному рядку (BL-20).»</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -4831,8 +4831,8 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>Варіант Горбонос О. (СМ): «До звернення можна додати один файл-вкладення розміром до 5 МБ у форматі PDF, PNG, JPG або TXT; для файлу, що не відповідає цим умовам, система показує повідомлення про недопустимий файл біля поля вкладення і не надсилає звернення (GUI-50).» (Формати й межа 5 МБ — потребує підтвердження замовником.)
-Варіант Тимчак А. (ТА): «… довжина повідомлення — від 50 до 250 символів. До звернення можна додати один файл формату .txt розміром до 500 КБ; для недопустимого файла звернення не надсилається, а біля поля виводиться повідомлення про помилку (GUI-50).»</t>
+          <t>Не внесено — Варіант Горбонос О. (СМ): «До звернення можна додати один файл-вкладення розміром до 5 МБ у форматі PDF, PNG, JPG або TXT; для файлу, що не відповідає цим умовам, система показує повідомлення про недопустимий файл біля поля вкладення і не надсилає звернення (GUI-50).» (Формати й межа 5 МБ — потребує підтвердження замовником.)
+ОБРАНО для SRS 1.1 — Варіант Тимчак А. (ТА): «… довжина повідомлення — від 50 до 250 символів. До звернення можна додати один файл формату .txt розміром до 500 КБ; для недопустимого файла звернення не надсилається, а біля поля виводиться повідомлення про помилку (GUI-50).»</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -5132,8 +5132,8 @@
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>Варіант Коротка К. (КТ): «Зображення товару на сторінці товару мають роздільну здатність не менше 1200×1200 пікселів, на картках каталогу — не менше 400×400 пікселів; за з'єднання 10 Мбіт/с зображення картки завантажується не довше ніж за 1 с.»
-Варіант Дрєпіна А. (ІТ): «Зображення товарів на картках каталогу і на сторінці товару оптимізуються для веб-середовища (роздільна здатність до 800x800 пікселів, формат WebP або JPEG, розмір до 250 КБ) і завантажуються не довше ніж за 1,5 с при швидкості підключення від 10 Мбіт/с (потребує підтвердження замовником).»</t>
+          <t>ОБРАНО для SRS 1.1 — Варіант Коротка К. (КТ): «Зображення товару на сторінці товару мають роздільну здатність не менше 1200×1200 пікселів, на картках каталогу — не менше 400×400 пікселів; за з'єднання 10 Мбіт/с зображення картки завантажується не довше ніж за 1 с.»
+Не внесено — Варіант Дрєпіна А. (ІТ): «Зображення товарів на картках каталогу і на сторінці товару оптимізуються для веб-середовища (роздільна здатність до 800x800 пікселів, формат WebP або JPEG, розмір до 250 КБ) і завантажуються не довше ніж за 1,5 с при швидкості підключення від 10 Мбіт/с (потребує підтвердження замовником).»</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -5233,8 +5233,8 @@
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t>Варіант Коротка К. (КТ): «Сторінка каталогу повністю завантажується не довше ніж за 3 с у 95 % вимірювань у Chrome 120 на настільному комп'ютері за з'єднання 10 Мбіт/с (20 вимірювань інструментом Lighthouse).»
-Варіант Дрєпіна А. (ІТ): «Час повного завантаження сторінки каталогу на настільних пристроях не перевищує 2,0 с при швидкості широкосмугового інтернет-з'єднання від 15 Мбіт/с; показник First Contentful Paint (FCP) становить не більше 1,0 с (потребує підтвердження замовником).»</t>
+          <t>ОБРАНО для SRS 1.1 — Варіант Коротка К. (КТ): «Сторінка каталогу повністю завантажується не довше ніж за 3 с у 95 % вимірювань у Chrome 120 на настільному комп'ютері за з'єднання 10 Мбіт/с (20 вимірювань інструментом Lighthouse).»
+Не внесено — Варіант Дрєпіна А. (ІТ): «Час повного завантаження сторінки каталогу на настільних пристроях не перевищує 2,0 с при швидкості широкосмугового інтернет-з'єднання від 15 Мбіт/с; показник First Contentful Paint (FCP) становить не більше 1,0 с (потребує підтвердження замовником).»</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -5284,8 +5284,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>Варіант Коротка К. (КТ): «Паролі покупців зберігаються лише у вигляді хешу bcrypt; сторінки й API доступні лише через HTTPS (запит по HTTP перенаправляється на HTTPS); запит до даних покупця Б з токеном покупця А повертає код 403.»
-Варіант Дрєпіна А. (ІТ): «Усі канали передачі персональних даних покупців захищені протоколом HTTPS (TLS 1.3); паролі зберігаються в базі даних виключно у хешованому вигляді (алгоритм bcrypt із сіллю); за результатами звіту сканування безпеки на локальному тестовому стенді розробників (на публічному demo сканування не проводиться) у релізі відсутні вразливості категорій Critical та High (потребує підтвердження замовником).»</t>
+          <t>ОБРАНО для SRS 1.1 (об'єднано варіанти КТ і ІТ, вибір ТА): «Паролі покупців зберігаються лише у вигляді хешу bcrypt (із сіллю); сторінки й API доступні лише через HTTPS (TLS 1.3), запит по HTTP перенаправляється на HTTPS; запит до даних покупця Б з токеном покупця А повертає код 403; за звітом сканування безпеки на локальному тестовому стенді розробників (на публічному demo сканування не проводиться) у релізі відсутні вразливості категорій Critical і High.»
+Вихідний — Варіант Коротка К. (КТ): «Паролі покупців зберігаються лише у вигляді хешу bcrypt; сторінки й API доступні лише через HTTPS (запит по HTTP перенаправляється на HTTPS); запит до даних покупця Б з токеном покупця А повертає код 403.»
+Вихідний — Варіант Дрєпіна А. (ІТ): «Усі канали передачі персональних даних покупців захищені протоколом HTTPS (TLS 1.3); паролі зберігаються в базі даних виключно у хешованому вигляді (алгоритм bcrypt із сіллю); за результатами звіту сканування безпеки на локальному тестовому стенді розробників (на публічному demo сканування не проводиться) у релізі відсутні вразливості категорій Critical та High (потребує підтвердження замовником).»</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -5335,8 +5336,8 @@
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>Варіант Коротка К. (КТ): «Новий користувач без інструкції знаходить товар пошуком, додає його в кошик і доходить до кроку «Payment» не довше ніж за 3 хв і не більше ніж з однією помилкою; перевірка на 5 учасниках, критерій — 4 з 5.»
-Варіант Дрєпіна А. (ІТ): «Новий користувач без попереднього інструктажу успішно проходить наскрізний чекаут не довше ніж за 3 хвилини; показник Task Success Rate становить не менше 90% при вибірці з 10 респондентів (потребує підтвердження замовником).»</t>
+          <t>Не внесено — Варіант Коротка К. (КТ): «Новий користувач без інструкції знаходить товар пошуком, додає його в кошик і доходить до кроку «Payment» не довше ніж за 3 хв і не більше ніж з однією помилкою; перевірка на 5 учасниках, критерій — 4 з 5.»
+ОБРАНО для SRS 1.1 — Варіант Дрєпіна А. (ІТ): «Новий користувач без попереднього інструктажу успішно проходить наскрізний чекаут не довше ніж за 3 хвилини; показник Task Success Rate становить не менше 90% при вибірці з 10 респондентів (потребує підтвердження замовником).»</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -8102,7 +8103,7 @@
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t>Ціль називає замовника; на demo не виконується — позначено.</t>
+          <t>Ціль називає замовника; на demo не виконується — позначено. Зовнішнє рев'ю 14.10.2026: Ціль прив'язано до критеріїв приймання продукту (без посилань на DoD спринта) — внесено в main (PR #35).</t>
         </is>
       </c>
       <c r="G44" s="22" t="n"/>
@@ -8246,7 +8247,7 @@
       </c>
       <c r="F48" s="22" t="inlineStr">
         <is>
-          <t>Редирект /account → /auth/login для гостя підтверджено на demo (12.10.2026); обмеження demo і позначки замовника є. Редакційне: S-20 вимагає також недоступності кроків 3–4 для гостя — додати крок.</t>
+          <t>Редирект /account → /auth/login для гостя підтверджено на demo (12.10.2026); обмеження demo і позначки замовника є. Редакційне: S-20 вимагає також недоступності кроків 3–4 для гостя — додати крок. Зовнішнє рев'ю 14.10.2026: додано перевірку доступу до чужих даних (S-10, код 403) — внесено в main (PR #35).</t>
         </is>
       </c>
       <c r="G48" s="22" t="n"/>
@@ -8406,20 +8407,24 @@
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
+          <t>1✗ 2✓ 3✓ 4✓ 5✓</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
         <is>
-          <t>пройшло</t>
+          <t>очікує КТ</t>
         </is>
       </c>
       <c r="F53" s="22" t="inlineStr">
         <is>
-          <t>Обмеження demo (52 товари, 6 сторінок, по 9) позначено й відповідає перевірці на demo.</t>
-        </is>
-      </c>
-      <c r="G53" s="22" t="n"/>
+          <t>Обмеження demo (52 товари, 6 сторінок, по 9) позначено й відповідає перевірці на demo. Зовнішнє рев'ю 14.10.2026: рядок описував функціональну перевірку F-40/F-50 на 52 товарах і не відповідав суті типу (об'ємне — коректність на великих обсягах даних); початкова оцінка «пройшло» була помилковою. Ціль і Опис переписано (кошик зі 100/1000/5000 рядків, звірка з еталоном, обхід усіх сторінок каталогу demo) і внесено в main (PR #35); повторне підтвердження — КТ.</t>
+        </is>
+      </c>
+      <c r="G53" s="22" t="inlineStr">
+        <is>
+          <t>14.10.2026 (ІТ, PR #35)</t>
+        </is>
+      </c>
       <c r="H53" s="22" t="n"/>
     </row>
     <row r="54">
@@ -9112,6 +9117,7 @@
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
@@ -9150,7 +9156,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Версії: перша перевірка — main (92899b6, 12.10.2026); повторна — main (1c0fea8, 13.10.2026: PR #23, #27, #28). Рецензент СМ: Горбонос О.</t>
+          <t>Версії: перша перевірка — main (92899b6, 12.10.2026); повторна — main (1c0fea8, 13.10.2026: PR #23, #27, #28); план після зовнішнього рев'ю — main (a5ce43d, 15.10.2026: PR #35). Рецензент СМ: Горбонос О.</t>
         </is>
       </c>
     </row>

--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -8407,17 +8407,17 @@
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>1✗ 2✓ 3✓ 4✓ 5✓</t>
+          <t>1✓ 2✓ 3✓ 4✓ 5✓</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
         <is>
-          <t>очікує КТ</t>
+          <t>пройшло</t>
         </is>
       </c>
       <c r="F53" s="22" t="inlineStr">
         <is>
-          <t>Обмеження demo (52 товари, 6 сторінок, по 9) позначено й відповідає перевірці на demo. Зовнішнє рев'ю 14.10.2026: рядок описував функціональну перевірку F-40/F-50 на 52 товарах і не відповідав суті типу (об'ємне — коректність на великих обсягах даних); початкова оцінка «пройшло» була помилковою. Ціль і Опис переписано (кошик зі 100/1000/5000 рядків, звірка з еталоном, обхід усіх сторінок каталогу demo) і внесено в main (PR #35); повторне підтвердження — КТ.</t>
+          <t>Обмеження demo (52 товари, 6 сторінок, по 9) позначено й відповідає перевірці на demo. Зовнішнє рев'ю 14.10.2026: рядок описував функціональну перевірку F-40/F-50 на 52 товарах і не відповідав суті типу (об'ємне — коректність на великих обсягах даних); початкова оцінка «пройшло» була помилковою. Ціль і Опис переписано (кошик зі 100/1000/5000 рядків, звірка з еталоном, обхід усіх сторінок каталогу demo) і внесено в main (PR #35); повторне підтвердження — КТ. Повторно перевірено КТ (Коротка К.) 15.10.2026: Ціль і Опис відповідають суті типу (великі обсяги даних: кошик 100/1000/5000 рядків з еталоном BigDecimal HALF_UP, каталог demo через API); пріоритет Medium і застосовність «Так» без змін. Редакційне: розміри вибірок 100/1000/5000 позначити «потребує підтвердження замовником», як авторські значення в типі 16.</t>
         </is>
       </c>
       <c r="G53" s="22" t="inlineStr">
@@ -8425,7 +8425,11 @@
           <t>14.10.2026 (ІТ, PR #35)</t>
         </is>
       </c>
-      <c r="H53" s="22" t="n"/>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>Коротка Ксенія (КТ), 15.10.2026</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
@@ -9117,7 +9121,6 @@
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
